--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -1082,7 +1082,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H32"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6"/>
   <cols>
     <col width="45" customWidth="1" min="1" max="1"/>
@@ -1103,7 +1103,27 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>26人 | 7/13确认 | 布格拉汗MCL | 凌中阳停赛 | 丁云峰未随队 | 刘子结试训</t>
+          <t>29人</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>7/17更新</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>布格拉汗MCL</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>凌中阳/丁云峰停赛(7/19)</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>刘子洁/董德/努尔扎提 7/17签约🆕</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1305,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>未随队（黄牌停赛结束·尚未归队）</t>
+          <t>跟队训练·停赛(7/19 vs大连英博B)</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1334,7 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>停赛在家（vs海港B延期·停赛移至7/19）</t>
+          <t>跟队训练·停赛(7/19 vs大连英博B)</t>
         </is>
       </c>
     </row>
@@ -1815,7 +1835,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>刘子结</t>
+          <t>刘子洁</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1825,7 +1845,56 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>试训球员·待确认</t>
+          <t>已签约(7/17)🆕</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>原试训</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>已签约(7/17)🆕</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>原试训</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>前锋</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>已签约(7/17)🆕</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>原试训</t>
         </is>
       </c>
     </row>

--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="10300" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="花名册" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,13 +17,59 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="21">
+  <fonts count="28">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
       <color theme="1"/>
       <sz val="12"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF992828"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF992828"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <color rgb="FFCC0000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FF228B22"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <color rgb="FFE67E00"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="宋体"/>
@@ -177,7 +223,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="33">
+  <fills count="43">
     <fill>
       <patternFill/>
     </fill>
@@ -186,6 +232,66 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF992828"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF555555"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF0E8E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0FFE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B5797"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE8D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228B22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE8DCDC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -371,12 +477,51 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="14">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFCCCCCC"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFCCCCCC"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -477,161 +622,241 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFCCCCCC"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFCCCCCC"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyAlignment="1">
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1082,825 +1307,1485 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
+  <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6"/>
   <cols>
-    <col width="45" customWidth="1" min="1" max="1"/>
-    <col width="32.1160714285714" customWidth="1" min="2" max="2"/>
-    <col width="8" customWidth="1" min="3" max="4"/>
-    <col width="10.8035714285714" customWidth="1" min="5" max="6"/>
-    <col width="17.4017857142857" customWidth="1" min="7" max="7"/>
-    <col width="8" customWidth="1" min="8" max="8"/>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="3" max="4"/>
+    <col width="8" customWidth="1" min="5" max="6"/>
+    <col width="42" customWidth="1" min="7" max="7"/>
+    <col width="50.2589285714286" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
+    <row r="1" ht="30" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>球员花名册 —— 山西崇德荣海 2026赛季</t>
         </is>
       </c>
     </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>29人</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>7/17更新</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>布格拉汗MCL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>凌中阳/丁云峰停赛(7/19)</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>刘子洁/董德/努尔扎提 7/17签约🆕</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="20" customHeight="1">
-      <c r="A3" s="1" t="inlineStr">
+    <row r="2" ht="22" customHeight="1">
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>31人 | 7/24更新 · 戚博→海门珂缔缘(租借) | ⚠️张俊哲RPE=8·王捷暂停离心</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" s="4" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
-      <c r="C3" s="1" t="inlineStr">
+      <c r="C3" s="4" t="inlineStr">
         <is>
           <t>号码</t>
         </is>
       </c>
-      <c r="D3" s="1" t="inlineStr">
+      <c r="D3" s="4" t="inlineStr">
         <is>
           <t>年龄</t>
         </is>
       </c>
-      <c r="E3" s="1" t="inlineStr">
+      <c r="E3" s="4" t="inlineStr">
         <is>
           <t>身高(cm)</t>
         </is>
       </c>
-      <c r="F3" s="1" t="inlineStr">
+      <c r="F3" s="4" t="inlineStr">
         <is>
           <t>体重(kg)</t>
         </is>
       </c>
-      <c r="G3" s="1" t="inlineStr">
+      <c r="G3" s="4" t="inlineStr">
         <is>
           <t>伤病/状态</t>
         </is>
       </c>
-      <c r="H3" s="1" t="inlineStr">
+      <c r="H3" s="4" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>门将 (4人)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+      <c r="G4" s="6" t="n"/>
+      <c r="H4" s="7" t="n"/>
+    </row>
+    <row r="5" ht="22" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
         <is>
           <t>张海轩</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B5" s="5" t="inlineStr">
         <is>
           <t>门将</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
-        <v>13</v>
-      </c>
-      <c r="D4" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E4" s="1" t="n">
-        <v>185</v>
-      </c>
-      <c r="F4" s="1" t="n">
-        <v>78</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>正常（腰痛已恢复✅）</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="D5" s="9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E5" s="9" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="F5" s="9" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G5" s="10" t="inlineStr">
+        <is>
+          <t>🔴脚踝痛D10·7/23 RPE=7</t>
+        </is>
+      </c>
+      <c r="H5" s="8" t="inlineStr">
+        <is>
+          <t>踝泵+冰敷·7/26可出战</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>杨卓燠</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B6" s="5" t="inlineStr">
         <is>
           <t>门将</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>31</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="E5" s="1" t="n">
-        <v>183</v>
-      </c>
-      <c r="F5" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>正常（腰痛7/12恢复✅）</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="20" customHeight="1">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D6" s="12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="E6" s="12" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="F6" s="12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G6" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23肩微疼</t>
+        </is>
+      </c>
+      <c r="H6" s="11" t="inlineStr"/>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="11" t="inlineStr">
         <is>
           <t>王款(U21)</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
+      <c r="B7" s="5" t="inlineStr">
         <is>
           <t>门将</t>
         </is>
       </c>
-      <c r="C6" s="1" t="n">
-        <v>15</v>
-      </c>
-      <c r="D6" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E6" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="F6" s="1" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="1" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="D7" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E7" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F7" s="12" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G7" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常</t>
+        </is>
+      </c>
+      <c r="H7" s="11" t="inlineStr"/>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="14" t="inlineStr">
+        <is>
+          <t>王熙博🆕</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>门将</t>
+        </is>
+      </c>
+      <c r="C8" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D8" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E8" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="16" t="inlineStr">
+        <is>
+          <t>🟢新人适应·7/23 RPE=5</t>
+        </is>
+      </c>
+      <c r="H8" s="14" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="17" t="inlineStr">
+        <is>
+          <t>后卫 (10人)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+      <c r="G9" s="6" t="n"/>
+      <c r="H9" s="7" t="n"/>
+    </row>
+    <row r="10" ht="22" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
         <is>
           <t>王捷(U21)</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
+      <c r="B10" s="17" t="inlineStr">
         <is>
           <t>后卫</t>
         </is>
       </c>
-      <c r="C7" s="1" t="n">
-        <v>4</v>
-      </c>
-      <c r="D7" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E7" s="1" t="n">
-        <v>178</v>
-      </c>
-      <c r="F7" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>⚠️左膝髌腱炎（7/13进入离心阶段）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="1" t="inlineStr">
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D10" s="9" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E10" s="9" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F10" s="9" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G10" s="10" t="inlineStr">
+        <is>
+          <t>🔴左膝髌腱炎·⚠️7/23酸痛1→4·暂停离心退回等长</t>
+        </is>
+      </c>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>7/25评估·赛前只做等长</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="11" t="inlineStr">
         <is>
           <t>丁云峰</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
+      <c r="B11" s="17" t="inlineStr">
         <is>
           <t>后卫</t>
         </is>
       </c>
-      <c r="C8" s="1" t="n">
-        <v>16</v>
-      </c>
-      <c r="D8" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E8" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="F8" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>跟队训练·停赛(7/19 vs大连英博B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="1" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D11" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E11" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F11" s="12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G11" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=7(正常酸痛)</t>
+        </is>
+      </c>
+      <c r="H11" s="11" t="inlineStr">
+        <is>
+          <t>停赛已结束·7/26可出战</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>凌中阳</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
+      <c r="B12" s="17" t="inlineStr">
         <is>
           <t>后卫</t>
         </is>
       </c>
-      <c r="C9" s="1" t="n">
-        <v>30</v>
-      </c>
-      <c r="D9" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="E9" s="1" t="n">
-        <v>182</v>
-      </c>
-      <c r="F9" s="1" t="n">
-        <v>75</v>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>跟队训练·停赛(7/19 vs大连英博B)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="1" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="D12" s="12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E12" s="12" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F12" s="12" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G12" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=7(三球门覆盖大)</t>
+        </is>
+      </c>
+      <c r="H12" s="11" t="inlineStr">
+        <is>
+          <t>停赛已结束·7/26可出战</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="11" t="inlineStr">
         <is>
           <t>陈少豪</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
+      <c r="B13" s="17" t="inlineStr">
         <is>
           <t>后卫</t>
         </is>
       </c>
-      <c r="C10" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="D10" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E10" s="1" t="n">
-        <v>181</v>
-      </c>
-      <c r="F10" s="1" t="n">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="1" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="D13" s="12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E13" s="12" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="F13" s="12" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="G13" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H13" s="11" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="18" t="inlineStr">
         <is>
           <t>李金羽</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
+      <c r="B14" s="17" t="inlineStr">
         <is>
           <t>后卫</t>
         </is>
       </c>
-      <c r="C11" s="1" t="n">
-        <v>22</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>正常（膝+腰7/12恢复✅）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="D14" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E14" s="19" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F14" s="19" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G14" s="20" t="inlineStr">
+        <is>
+          <t>🟠⚠️ 7/23 RPE=7·连续两天偏高·睡3疲3</t>
+        </is>
+      </c>
+      <c r="H14" s="18" t="inlineStr">
+        <is>
+          <t>关注恢复</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="18" t="inlineStr">
         <is>
           <t>王皓文(U21)</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
+      <c r="B15" s="17" t="inlineStr">
         <is>
           <t>后卫</t>
         </is>
       </c>
-      <c r="C12" s="1" t="n">
-        <v>24</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>178</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>70</v>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>正常（小腿酸痛7/13已恢复✅）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="1" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D15" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E15" s="19" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F15" s="19" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
+      <c r="G15" s="20" t="inlineStr">
+        <is>
+          <t>🟠7/23 RPE=7(正常酸痛)</t>
+        </is>
+      </c>
+      <c r="H15" s="18" t="inlineStr">
+        <is>
+          <t>7/19打满95min·恢复中</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="18" t="inlineStr">
+        <is>
+          <t>张俊哲</t>
+        </is>
+      </c>
+      <c r="B16" s="17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="D16" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="E16" s="19" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="F16" s="19" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="G16" s="20" t="inlineStr">
+        <is>
+          <t>🔴⚠️⚠️⚠️ 7/23 RPE=8全队最高·累积疲劳</t>
+        </is>
+      </c>
+      <c r="H16" s="18" t="inlineStr">
+        <is>
+          <t>7/19跑10km+7/22全量力量→D-3/D-2必须降量·软组织放松</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="11" t="inlineStr">
+        <is>
+          <t>张天龙</t>
+        </is>
+      </c>
+      <c r="B17" s="17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C17" s="12" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="D17" s="12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E17" s="12" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="F17" s="12" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="G17" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=5</t>
+        </is>
+      </c>
+      <c r="H17" s="11" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="11" t="inlineStr">
+        <is>
+          <t>杨文杰</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C18" s="12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=6(4v4+主组)</t>
+        </is>
+      </c>
+      <c r="H18" s="11" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
+        <is>
+          <t>刘子洁</t>
+        </is>
+      </c>
+      <c r="B19" s="17" t="inlineStr">
+        <is>
+          <t>后卫</t>
+        </is>
+      </c>
+      <c r="C19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F19" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G19" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 4v4组·RPE=5</t>
+        </is>
+      </c>
+      <c r="H19" s="11" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>中场 (12人·含边前卫1)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n"/>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n"/>
+      <c r="F20" s="6" t="n"/>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="7" t="n"/>
+    </row>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="11" t="inlineStr">
         <is>
           <t>杨翼璇</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="n">
-        <v>23</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>175</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>张俊哲</t>
-        </is>
-      </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="n">
-        <v>60</v>
-      </c>
-      <c r="D14" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="E14" s="1" t="n">
-        <v>182</v>
-      </c>
-      <c r="F14" s="1" t="n">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>张天龙</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="n">
-        <v>39</v>
-      </c>
-      <c r="D15" s="1" t="n">
-        <v>28</v>
-      </c>
-      <c r="E15" s="1" t="n">
-        <v>180</v>
-      </c>
-      <c r="F15" s="1" t="n">
-        <v>73</v>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>正常（腘绳肌7/12恢复✅）</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="1" t="inlineStr">
+      <c r="B21" s="21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C21" s="12" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="D21" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E21" s="12" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F21" s="12" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G21" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=5</t>
+        </is>
+      </c>
+      <c r="H21" s="11" t="inlineStr"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="18" t="inlineStr">
         <is>
           <t>何麟立</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
+      <c r="B22" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C16" s="1" t="n">
-        <v>55</v>
-      </c>
-      <c r="D16" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E16" s="1" t="n">
-        <v>175</v>
-      </c>
-      <c r="F16" s="1" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="1" t="inlineStr">
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D22" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E22" s="19" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F22" s="19" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>🟢正常·睡眠5→2✅·腘绳肌已恢复</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
         <is>
           <t>布格拉汗-斯坎旦尔</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
+      <c r="B23" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C17" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="D17" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E17" s="1" t="n">
-        <v>172</v>
-      </c>
-      <c r="F17" s="1" t="n">
-        <v>65</v>
-      </c>
-      <c r="G17" s="1" t="inlineStr">
-        <is>
-          <t>⚠️MCL撕裂 伤停</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="1" t="inlineStr">
+      <c r="C23" s="9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D23" s="9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E23" s="9" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F23" s="9" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G23" s="10" t="inlineStr">
+        <is>
+          <t>🔴MCL·⚡D+2·4v4完成✅·变向可控·进度超前</t>
+        </is>
+      </c>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>继续康复方案·冰敷·MCL抗外翻</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
         <is>
           <t>巫林峰</t>
         </is>
       </c>
-      <c r="B18" s="1" t="inlineStr">
+      <c r="B24" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C18" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="D18" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E18" s="1" t="n">
-        <v>175</v>
-      </c>
-      <c r="F18" s="1" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="1" t="inlineStr">
+      <c r="C24" s="9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D24" s="9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E24" s="9" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F24" s="9" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G24" s="10" t="inlineStr">
+        <is>
+          <t>🟢正常·脚掌无新信号·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H24" s="8" t="inlineStr"/>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="18" t="inlineStr">
         <is>
           <t>张辉</t>
         </is>
       </c>
-      <c r="B19" s="1" t="inlineStr">
+      <c r="B25" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C19" s="1" t="n">
-        <v>38</v>
-      </c>
-      <c r="D19" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E19" s="1" t="n">
-        <v>176</v>
-      </c>
-      <c r="F19" s="1" t="n">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="1" t="inlineStr">
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D25" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E25" s="19" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="F25" s="19" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="G25" s="20" t="inlineStr">
+        <is>
+          <t>🟠⚠️ 7/23 RPE=7·肌肉酸·脚腕疼史</t>
+        </is>
+      </c>
+      <c r="H25" s="18" t="inlineStr">
+        <is>
+          <t>10km组·累积疲劳·监控</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="11" t="inlineStr">
         <is>
           <t>谢锦政</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
+      <c r="B26" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C20" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="D20" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E20" s="1" t="n">
-        <v>174</v>
-      </c>
-      <c r="F20" s="1" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="1" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="D26" s="12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E26" s="12" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="F26" s="12" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G26" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·内踝7/22已恢复✅</t>
+        </is>
+      </c>
+      <c r="H26" s="11" t="inlineStr">
+        <is>
+          <t>7/26可全力</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="11" t="inlineStr">
         <is>
           <t>栾昊(U21)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
+      <c r="B27" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C21" s="1" t="n">
-        <v>8</v>
-      </c>
-      <c r="D21" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E21" s="1" t="n">
-        <v>173</v>
-      </c>
-      <c r="F21" s="1" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="1" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D27" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E27" s="12" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F27" s="12" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G27" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H27" s="11" t="inlineStr"/>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="11" t="inlineStr">
         <is>
           <t>林楷轩(U21)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
+      <c r="B28" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C22" s="1" t="n">
-        <v>27</v>
-      </c>
-      <c r="D22" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E22" s="1" t="n">
-        <v>172</v>
-      </c>
-      <c r="F22" s="1" t="n">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="1" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D28" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="E28" s="12" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F28" s="12" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="G28" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·4v4组·酸痛=4(正常反应)</t>
+        </is>
+      </c>
+      <c r="H28" s="11" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="11" t="inlineStr">
         <is>
           <t>朱云天(U21)</t>
         </is>
       </c>
-      <c r="B23" s="1" t="inlineStr">
+      <c r="B29" s="21" t="inlineStr">
         <is>
           <t>中场</t>
         </is>
       </c>
-      <c r="C23" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="D23" s="1" t="n">
-        <v>19</v>
-      </c>
-      <c r="E23" s="1" t="n">
-        <v>172</v>
-      </c>
-      <c r="F23" s="1" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>杨文杰</t>
-        </is>
-      </c>
-      <c r="B24" s="1" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C24" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
-      <c r="E24" s="2" t="n"/>
-      <c r="F24" s="2" t="n"/>
-    </row>
-    <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="1" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="D29" s="12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="E29" s="12" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F29" s="12" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G29" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·4v4组·RPE=4</t>
+        </is>
+      </c>
+      <c r="H29" s="11" t="inlineStr"/>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>董德</t>
+        </is>
+      </c>
+      <c r="B30" s="21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>🟠⚠️ 睡4+RPE=2·投入度待观察</t>
+        </is>
+      </c>
+      <c r="H30" s="11" t="inlineStr">
+        <is>
+          <t>新人·建议沟通</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="14" t="inlineStr">
+        <is>
+          <t>吕佳骏🆕</t>
+        </is>
+      </c>
+      <c r="B31" s="21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G31" s="16" t="inlineStr">
+        <is>
+          <t>🟢新人适应·4v4组·10min替换</t>
+        </is>
+      </c>
+      <c r="H31" s="14" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>薛悦伟🆕</t>
+        </is>
+      </c>
+      <c r="B32" s="21" t="inlineStr">
+        <is>
+          <t>中场</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G32" s="16" t="inlineStr">
+        <is>
+          <t>🟠新人·数据全部缺填</t>
+        </is>
+      </c>
+      <c r="H32" s="14" t="inlineStr">
+        <is>
+          <t>提醒补填</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="22" t="inlineStr">
+        <is>
+          <t>前锋 (5人)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n"/>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+      <c r="G33" s="6" t="n"/>
+      <c r="H33" s="7" t="n"/>
+    </row>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="18" t="inlineStr">
         <is>
           <t>陈祥煜</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
+      <c r="B34" s="22" t="inlineStr">
         <is>
           <t>前锋</t>
         </is>
       </c>
-      <c r="C25" s="1" t="n">
-        <v>33</v>
-      </c>
-      <c r="D25" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E25" s="1" t="n">
-        <v>178</v>
-      </c>
-      <c r="F25" s="1" t="n">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="1" t="inlineStr">
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="D34" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E34" s="19" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="F34" s="19" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="G34" s="20" t="inlineStr">
+        <is>
+          <t>🟢正常·恢复良好✅·7/23 RPE=5</t>
+        </is>
+      </c>
+      <c r="H34" s="18" t="inlineStr"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
         <is>
           <t>艾沙江-库尔班</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
+      <c r="B35" s="22" t="inlineStr">
         <is>
           <t>前锋</t>
         </is>
       </c>
-      <c r="C26" s="1" t="n">
-        <v>7</v>
-      </c>
-      <c r="D26" s="1" t="n">
-        <v>26</v>
-      </c>
-      <c r="E26" s="1" t="n">
-        <v>173</v>
-      </c>
-      <c r="F26" s="1" t="n">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="27" ht="20" customHeight="1">
-      <c r="A27" s="1" t="inlineStr">
+      <c r="C35" s="9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="D35" s="9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="E35" s="9" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="F35" s="9" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="G35" s="10" t="inlineStr">
+        <is>
+          <t>🟠左后群紧·持续监控·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="inlineStr">
+        <is>
+          <t>训练前激活·赛前三步自测</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="18" t="inlineStr">
         <is>
           <t>帕尔曼江-克尤木</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
+      <c r="B36" s="22" t="inlineStr">
         <is>
           <t>前锋</t>
         </is>
       </c>
-      <c r="C27" s="1" t="n">
-        <v>9</v>
-      </c>
-      <c r="D27" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E27" s="1" t="n">
-        <v>172</v>
-      </c>
-      <c r="F27" s="1" t="n">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="1" t="inlineStr">
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="D36" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E36" s="19" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="F36" s="19" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="G36" s="20" t="inlineStr">
+        <is>
+          <t>🟠睡眠4→3改善·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr"/>
+    </row>
+    <row r="37" ht="22" customHeight="1">
+      <c r="A37" s="18" t="inlineStr">
         <is>
           <t>阿西江-白山</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
+      <c r="B37" s="22" t="inlineStr">
         <is>
           <t>前锋</t>
         </is>
       </c>
-      <c r="C28" s="1" t="n">
-        <v>14</v>
-      </c>
-      <c r="D28" s="1" t="n">
-        <v>25</v>
-      </c>
-      <c r="E28" s="1" t="n">
-        <v>175</v>
-      </c>
-      <c r="F28" s="1" t="n">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>戚博(U21)</t>
-        </is>
-      </c>
-      <c r="B29" s="1" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="D37" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="E37" s="19" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F37" s="19" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G37" s="20" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H37" s="18" t="inlineStr"/>
+    </row>
+    <row r="38" ht="22" customHeight="1">
+      <c r="A38" s="11" t="inlineStr">
+        <is>
+          <t>努尔扎提-努尔兰</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
         <is>
           <t>前锋</t>
         </is>
       </c>
-      <c r="C29" s="1" t="n">
-        <v>36</v>
-      </c>
-      <c r="D29" s="1" t="n">
-        <v>20</v>
-      </c>
-      <c r="E29" s="1" t="n">
-        <v>175</v>
-      </c>
-      <c r="F29" s="1" t="n">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>刘子洁</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>已签约(7/17)🆕</t>
-        </is>
-      </c>
-      <c r="H30" t="inlineStr">
-        <is>
-          <t>原试训</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>董德</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>已签约(7/17)🆕</t>
-        </is>
-      </c>
-      <c r="H31" t="inlineStr">
-        <is>
-          <t>原试训</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>努尔扎提-努尔兰</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr">
-        <is>
-          <t>已签约(7/17)🆕</t>
-        </is>
-      </c>
-      <c r="H32" t="inlineStr">
-        <is>
-          <t>原试训</t>
-        </is>
-      </c>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G38" s="13" t="inlineStr">
+        <is>
+          <t>🟢正常·7/23 RPE=6</t>
+        </is>
+      </c>
+      <c r="H38" s="11" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="23" t="n"/>
+      <c r="B39" s="23" t="n"/>
+      <c r="C39" s="23" t="n"/>
+      <c r="D39" s="23" t="n"/>
+      <c r="E39" s="23" t="n"/>
+      <c r="F39" s="23" t="n"/>
+      <c r="G39" s="23" t="n"/>
+      <c r="H39" s="23" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="inlineStr">
+        <is>
+          <t>31人: 门将4 | 后卫10 | 中场12(含边前卫1) | 前锋5 | 🟢正常18 🟠降量8 🔴康复5 | 7/21更新</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="23" t="n"/>
+      <c r="B41" s="23" t="n"/>
+      <c r="C41" s="23" t="n"/>
+      <c r="D41" s="23" t="n"/>
+      <c r="E41" s="23" t="n"/>
+      <c r="F41" s="23" t="n"/>
+      <c r="G41" s="23" t="n"/>
+      <c r="H41" s="23" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="23" t="n"/>
+      <c r="B42" s="23" t="n"/>
+      <c r="C42" s="23" t="n"/>
+      <c r="D42" s="23" t="n"/>
+      <c r="E42" s="23" t="n"/>
+      <c r="F42" s="23" t="n"/>
+      <c r="G42" s="23" t="n"/>
+      <c r="H42" s="23" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="23" t="n"/>
+      <c r="B43" s="23" t="n"/>
+      <c r="C43" s="23" t="n"/>
+      <c r="D43" s="23" t="n"/>
+      <c r="E43" s="23" t="n"/>
+      <c r="F43" s="23" t="n"/>
+      <c r="G43" s="23" t="n"/>
+      <c r="H43" s="23" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="23" t="n"/>
+      <c r="B44" s="23" t="n"/>
+      <c r="C44" s="23" t="n"/>
+      <c r="D44" s="23" t="n"/>
+      <c r="E44" s="23" t="n"/>
+      <c r="F44" s="23" t="n"/>
+      <c r="G44" s="23" t="n"/>
+      <c r="H44" s="23" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="23" t="n"/>
+      <c r="B45" s="23" t="n"/>
+      <c r="C45" s="23" t="n"/>
+      <c r="D45" s="23" t="n"/>
+      <c r="E45" s="23" t="n"/>
+      <c r="F45" s="23" t="n"/>
+      <c r="G45" s="23" t="n"/>
+      <c r="H45" s="23" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="23" t="n"/>
+      <c r="B46" s="23" t="n"/>
+      <c r="C46" s="23" t="n"/>
+      <c r="D46" s="23" t="n"/>
+      <c r="E46" s="23" t="n"/>
+      <c r="F46" s="23" t="n"/>
+      <c r="G46" s="23" t="n"/>
+      <c r="H46" s="23" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="23" t="n"/>
+      <c r="B47" s="23" t="n"/>
+      <c r="C47" s="23" t="n"/>
+      <c r="D47" s="23" t="n"/>
+      <c r="E47" s="23" t="n"/>
+      <c r="F47" s="23" t="n"/>
+      <c r="G47" s="23" t="n"/>
+      <c r="H47" s="23" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="23" t="n"/>
+      <c r="B48" s="23" t="n"/>
+      <c r="C48" s="23" t="n"/>
+      <c r="D48" s="23" t="n"/>
+      <c r="E48" s="23" t="n"/>
+      <c r="F48" s="23" t="n"/>
+      <c r="G48" s="23" t="n"/>
+      <c r="H48" s="23" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="23" t="n"/>
+      <c r="B49" s="23" t="n"/>
+      <c r="C49" s="23" t="n"/>
+      <c r="D49" s="23" t="n"/>
+      <c r="E49" s="23" t="n"/>
+      <c r="F49" s="23" t="n"/>
+      <c r="G49" s="23" t="n"/>
+      <c r="H49" s="23" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="23" t="n"/>
+      <c r="B50" s="23" t="n"/>
+      <c r="C50" s="23" t="n"/>
+      <c r="D50" s="23" t="n"/>
+      <c r="E50" s="23" t="n"/>
+      <c r="F50" s="23" t="n"/>
+      <c r="G50" s="23" t="n"/>
+      <c r="H50" s="23" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:B2"/>
+  <mergeCells count="7">
+    <mergeCell ref="A9:H9"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A20:H20"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A33:H33"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A40:H40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="28">
+  <fonts count="34">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -222,8 +222,38 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00992828"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <color rgb="00888888"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
   </fonts>
-  <fills count="43">
+  <fills count="48">
     <fill>
       <patternFill/>
     </fill>
@@ -476,8 +506,38 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00992828"/>
+        <bgColor rgb="00992828"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5F5F5"/>
+        <bgColor rgb="00F5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFD9B3"/>
+        <bgColor rgb="00FFD9B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+        <bgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="001a1f2e"/>
+        <bgColor rgb="001a1f2e"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="14">
+  <borders count="19">
     <border>
       <left/>
       <right/>
@@ -642,6 +702,40 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -790,7 +884,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -857,6 +951,75 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="30" fillId="43" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="44" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="44" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="45" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="46" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="33" fillId="47" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1311,24 +1474,26 @@
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="6" customWidth="1" min="2" max="2"/>
     <col width="6" customWidth="1" min="3" max="4"/>
+    <col width="6" customWidth="1" min="4" max="4"/>
     <col width="8" customWidth="1" min="5" max="6"/>
-    <col width="42" customWidth="1" min="7" max="7"/>
-    <col width="50.2589285714286" customWidth="1" min="8" max="8"/>
+    <col width="8" customWidth="1" min="6" max="6"/>
+    <col width="40" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="2" t="inlineStr">
-        <is>
-          <t>球员花名册 —— 山西崇德荣海 2026赛季</t>
+      <c r="A1" s="25" t="inlineStr">
+        <is>
+          <t>崇德荣海 · 球员花名册 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>31人 | 7/24更新 · 戚博→海门珂缔缘(租借) | ⚠️张俊哲RPE=8·王捷暂停离心</t>
+      <c r="A2" s="26" t="inlineStr">
+        <is>
+          <t>30人 · 8/8 · 戚博→海门珂缔缘(租借) · 8/5客1-0海港B · 8/8 MD-1 · 明客vs长春喜都</t>
         </is>
       </c>
     </row>
@@ -1375,1176 +1540,973 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>门将 (4人)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n"/>
-      <c r="C4" s="6" t="n"/>
-      <c r="D4" s="6" t="n"/>
-      <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
-      <c r="G4" s="6" t="n"/>
-      <c r="H4" s="7" t="n"/>
+      <c r="A4" s="27" t="inlineStr">
+        <is>
+          <t>姓名</t>
+        </is>
+      </c>
+      <c r="B4" s="27" t="inlineStr">
+        <is>
+          <t>位置</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="inlineStr">
+        <is>
+          <t>号码</t>
+        </is>
+      </c>
+      <c r="D4" s="27" t="inlineStr">
+        <is>
+          <t>年龄</t>
+        </is>
+      </c>
+      <c r="E4" s="27" t="inlineStr">
+        <is>
+          <t>身高</t>
+        </is>
+      </c>
+      <c r="F4" s="27" t="inlineStr">
+        <is>
+          <t>体重</t>
+        </is>
+      </c>
+      <c r="G4" s="27" t="inlineStr">
+        <is>
+          <t>伤病/状态</t>
+        </is>
+      </c>
+      <c r="H4" s="27" t="inlineStr">
+        <is>
+          <t>备注</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="48" t="inlineStr">
+        <is>
+          <t>门将 4人</t>
+        </is>
+      </c>
+      <c r="B5" s="46" t="n"/>
+      <c r="C5" s="46" t="n"/>
+      <c r="D5" s="46" t="n"/>
+      <c r="E5" s="46" t="n"/>
+      <c r="F5" s="46" t="n"/>
+      <c r="G5" s="46" t="n"/>
+      <c r="H5" s="47" t="n"/>
+    </row>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="30" t="inlineStr">
         <is>
           <t>张海轩</t>
         </is>
       </c>
-      <c r="B5" s="5" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="D5" s="9" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E5" s="9" t="inlineStr">
-        <is>
-          <t>185</t>
-        </is>
-      </c>
-      <c r="F5" s="9" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="G5" s="10" t="inlineStr">
-        <is>
-          <t>🔴脚踝痛D10·7/23 RPE=7</t>
-        </is>
-      </c>
-      <c r="H5" s="8" t="inlineStr">
-        <is>
-          <t>踝泵+冰敷·7/26可出战</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="11" t="inlineStr">
+      <c r="B6" s="31" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C6" s="31" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="E6" s="31" t="n">
+        <v>185</v>
+      </c>
+      <c r="F6" s="31" t="n">
+        <v>78</v>
+      </c>
+      <c r="G6" s="32" t="inlineStr">
+        <is>
+          <t>🔴脚踝痛D3·今日RPE=4·疲5→2✅·酸4→1✅</t>
+        </is>
+      </c>
+      <c r="H6" s="31" t="inlineStr">
+        <is>
+          <t>赛前评估·可出战</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="22" customHeight="1">
+      <c r="A7" s="33" t="inlineStr">
         <is>
           <t>杨卓燠</t>
         </is>
       </c>
-      <c r="B6" s="5" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="C6" s="12" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="D6" s="12" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="E6" s="12" t="inlineStr">
-        <is>
-          <t>183</t>
-        </is>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G6" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23肩微疼</t>
-        </is>
-      </c>
-      <c r="H6" s="11" t="inlineStr"/>
-    </row>
-    <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="B7" s="34" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C7" s="35" t="n">
+        <v>31</v>
+      </c>
+      <c r="D7" s="35" t="n">
+        <v>24</v>
+      </c>
+      <c r="E7" s="35" t="n">
+        <v>183</v>
+      </c>
+      <c r="F7" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="G7" s="36" t="inlineStr">
+        <is>
+          <t>🟡腰疼D2·今日RPE=3</t>
+        </is>
+      </c>
+      <c r="H7" s="35" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1">
+      <c r="A8" s="30" t="inlineStr">
         <is>
           <t>王款(U21)</t>
         </is>
       </c>
-      <c r="B7" s="5" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="C7" s="12" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="D7" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E7" s="12" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F7" s="12" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G7" s="13" t="inlineStr">
+      <c r="B8" s="31" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C8" s="31" t="n">
+        <v>15</v>
+      </c>
+      <c r="D8" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E8" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="F8" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="G8" s="31" t="inlineStr">
         <is>
           <t>🟢正常</t>
         </is>
       </c>
-      <c r="H7" s="11" t="inlineStr"/>
-    </row>
-    <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="14" t="inlineStr">
-        <is>
-          <t>王熙博🆕</t>
-        </is>
-      </c>
-      <c r="B8" s="5" t="inlineStr">
-        <is>
-          <t>门将</t>
-        </is>
-      </c>
-      <c r="C8" s="15" t="inlineStr">
+      <c r="H8" s="31" t="inlineStr"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="37" t="inlineStr">
+        <is>
+          <t>王熙博</t>
+        </is>
+      </c>
+      <c r="B9" s="35" t="inlineStr">
+        <is>
+          <t>GK</t>
+        </is>
+      </c>
+      <c r="C9" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D8" s="15" t="inlineStr">
+      <c r="D9" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E8" s="15" t="inlineStr">
+      <c r="E9" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F8" s="15" t="inlineStr">
+      <c r="F9" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G8" s="16" t="inlineStr">
-        <is>
-          <t>🟢新人适应·7/23 RPE=5</t>
-        </is>
-      </c>
-      <c r="H8" s="14" t="inlineStr"/>
-    </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
-        <is>
-          <t>后卫 (10人)</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n"/>
-      <c r="C9" s="6" t="n"/>
-      <c r="D9" s="6" t="n"/>
-      <c r="E9" s="6" t="n"/>
-      <c r="F9" s="6" t="n"/>
-      <c r="G9" s="6" t="n"/>
-      <c r="H9" s="7" t="n"/>
+      <c r="G9" s="35" t="inlineStr">
+        <is>
+          <t>🟢新人适应·未赴沪</t>
+        </is>
+      </c>
+      <c r="H9" s="35" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="49" t="inlineStr">
+        <is>
+          <t>后卫 10人</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n"/>
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="7" t="n"/>
+    </row>
+    <row r="11" ht="22" customHeight="1">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>王捷(U21)</t>
         </is>
       </c>
-      <c r="B10" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D10" s="9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="F10" s="9" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>🔴左膝髌腱炎·⚠️7/23酸痛1→4·暂停离心退回等长</t>
-        </is>
-      </c>
-      <c r="H10" s="8" t="inlineStr">
-        <is>
-          <t>7/25评估·赛前只做等长</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>4</v>
+      </c>
+      <c r="D11" t="n">
+        <v>20</v>
+      </c>
+      <c r="E11" t="n">
+        <v>178</v>
+      </c>
+      <c r="F11" t="n">
+        <v>70</v>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>🟡左膝髌腱炎·今日RPE=2·疲3</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>赛前等长</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1">
+      <c r="A12" s="30" t="inlineStr">
         <is>
           <t>丁云峰</t>
         </is>
       </c>
-      <c r="B11" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C11" s="12" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="D11" s="12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E11" s="12" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F11" s="12" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G11" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=7(正常酸痛)</t>
-        </is>
-      </c>
-      <c r="H11" s="11" t="inlineStr">
-        <is>
-          <t>停赛已结束·7/26可出战</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+      <c r="B12" s="31" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C12" s="31" t="n">
+        <v>16</v>
+      </c>
+      <c r="D12" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E12" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="F12" s="31" t="n">
+        <v>73</v>
+      </c>
+      <c r="G12" s="32" t="inlineStr">
+        <is>
+          <t>🟢正常·今日RPE=3</t>
+        </is>
+      </c>
+      <c r="H12" s="31" t="inlineStr"/>
+    </row>
+    <row r="13" ht="22" customHeight="1">
+      <c r="A13" s="33" t="inlineStr">
         <is>
           <t>凌中阳</t>
         </is>
       </c>
-      <c r="B12" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C12" s="12" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="D12" s="12" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E12" s="12" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="F12" s="12" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G12" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=7(三球门覆盖大)</t>
-        </is>
-      </c>
-      <c r="H12" s="11" t="inlineStr">
-        <is>
-          <t>停赛已结束·7/26可出战</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="11" t="inlineStr">
+      <c r="B13" s="38" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C13" s="35" t="n">
+        <v>30</v>
+      </c>
+      <c r="D13" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="E13" s="35" t="n">
+        <v>182</v>
+      </c>
+      <c r="F13" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="G13" s="36" t="inlineStr">
+        <is>
+          <t>🟢正常·今日RPE=3</t>
+        </is>
+      </c>
+      <c r="H13" s="35" t="inlineStr"/>
+    </row>
+    <row r="14" ht="22" customHeight="1">
+      <c r="A14" s="30" t="inlineStr">
         <is>
           <t>陈少豪</t>
         </is>
       </c>
-      <c r="B13" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="D13" s="12" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="F13" s="12" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="G13" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H13" s="11" t="inlineStr"/>
-    </row>
-    <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="18" t="inlineStr">
+      <c r="B14" s="31" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C14" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="D14" s="31" t="n">
+        <v>26</v>
+      </c>
+      <c r="E14" s="31" t="n">
+        <v>181</v>
+      </c>
+      <c r="F14" s="31" t="n">
+        <v>74</v>
+      </c>
+      <c r="G14" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·今日RPE=2</t>
+        </is>
+      </c>
+      <c r="H14" s="31" t="inlineStr"/>
+    </row>
+    <row r="15" ht="22" customHeight="1">
+      <c r="A15" s="33" t="inlineStr">
         <is>
           <t>李金羽</t>
         </is>
       </c>
-      <c r="B14" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F14" s="19" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G14" s="20" t="inlineStr">
-        <is>
-          <t>🟠⚠️ 7/23 RPE=7·连续两天偏高·睡3疲3</t>
-        </is>
-      </c>
-      <c r="H14" s="18" t="inlineStr">
-        <is>
-          <t>关注恢复</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="18" t="inlineStr">
+      <c r="B15" s="38" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C15" s="35" t="n">
+        <v>22</v>
+      </c>
+      <c r="D15" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="E15" s="35" t="n">
+        <v>180</v>
+      </c>
+      <c r="F15" s="35" t="n">
+        <v>73</v>
+      </c>
+      <c r="G15" s="39" t="inlineStr">
+        <is>
+          <t>🟢正常·今日RPE=2·右膝已恢复✅</t>
+        </is>
+      </c>
+      <c r="H15" s="35" t="inlineStr"/>
+    </row>
+    <row r="16" ht="22" customHeight="1">
+      <c r="A16" s="30" t="inlineStr">
         <is>
           <t>王皓文(U21)</t>
         </is>
       </c>
-      <c r="B15" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="F15" s="19" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
-      <c r="G15" s="20" t="inlineStr">
-        <is>
-          <t>🟠7/23 RPE=7(正常酸痛)</t>
-        </is>
-      </c>
-      <c r="H15" s="18" t="inlineStr">
-        <is>
-          <t>7/19打满95min·恢复中</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="18" t="inlineStr">
+      <c r="B16" s="31" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C16" s="31" t="n">
+        <v>24</v>
+      </c>
+      <c r="D16" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E16" s="31" t="n">
+        <v>178</v>
+      </c>
+      <c r="F16" s="31" t="n">
+        <v>70</v>
+      </c>
+      <c r="G16" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5首发全场RPE=9</t>
+        </is>
+      </c>
+      <c r="H16" s="31" t="inlineStr"/>
+    </row>
+    <row r="17" ht="22" customHeight="1">
+      <c r="A17" s="33" t="inlineStr">
         <is>
           <t>张俊哲</t>
         </is>
       </c>
-      <c r="B16" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>182</t>
-        </is>
-      </c>
-      <c r="F16" s="19" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="G16" s="20" t="inlineStr">
-        <is>
-          <t>🔴⚠️⚠️⚠️ 7/23 RPE=8全队最高·累积疲劳</t>
-        </is>
-      </c>
-      <c r="H16" s="18" t="inlineStr">
-        <is>
-          <t>7/19跑10km+7/22全量力量→D-3/D-2必须降量·软组织放松</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+      <c r="B17" s="38" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C17" s="35" t="n">
+        <v>60</v>
+      </c>
+      <c r="D17" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="E17" s="35" t="n">
+        <v>182</v>
+      </c>
+      <c r="F17" s="35" t="n">
+        <v>75</v>
+      </c>
+      <c r="G17" s="36" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5首发92'满分</t>
+        </is>
+      </c>
+      <c r="H17" s="35" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="A18" s="30" t="inlineStr">
         <is>
           <t>张天龙</t>
         </is>
       </c>
-      <c r="B17" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="inlineStr">
-        <is>
-          <t>39</t>
-        </is>
-      </c>
-      <c r="D17" s="12" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="F17" s="12" t="inlineStr">
-        <is>
-          <t>73</t>
-        </is>
-      </c>
-      <c r="G17" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=5</t>
-        </is>
-      </c>
-      <c r="H17" s="11" t="inlineStr"/>
-    </row>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="11" t="inlineStr">
+      <c r="B18" s="31" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C18" s="31" t="n">
+        <v>39</v>
+      </c>
+      <c r="D18" s="31" t="n">
+        <v>28</v>
+      </c>
+      <c r="E18" s="31" t="n">
+        <v>180</v>
+      </c>
+      <c r="F18" s="31" t="n">
+        <v>73</v>
+      </c>
+      <c r="G18" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5首发全场</t>
+        </is>
+      </c>
+      <c r="H18" s="31" t="inlineStr"/>
+    </row>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="33" t="inlineStr">
         <is>
           <t>杨文杰</t>
         </is>
       </c>
-      <c r="B18" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C18" s="12" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="D18" s="12" t="inlineStr">
+      <c r="B19" s="38" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C19" s="35" t="n">
+        <v>5</v>
+      </c>
+      <c r="D19" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E18" s="12" t="inlineStr">
+      <c r="E19" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F18" s="12" t="inlineStr">
+      <c r="F19" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G18" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=6(4v4+主组)</t>
-        </is>
-      </c>
-      <c r="H18" s="11" t="inlineStr"/>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+      <c r="G19" s="36" t="inlineStr">
+        <is>
+          <t>🟢正常</t>
+        </is>
+      </c>
+      <c r="H19" s="35" t="inlineStr"/>
+    </row>
+    <row r="20" ht="20" customHeight="1">
+      <c r="A20" s="30" t="inlineStr">
         <is>
           <t>刘子洁</t>
         </is>
       </c>
-      <c r="B19" s="17" t="inlineStr">
-        <is>
-          <t>后卫</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="inlineStr">
+      <c r="B20" s="31" t="inlineStr">
+        <is>
+          <t>DEF</t>
+        </is>
+      </c>
+      <c r="C20" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D19" s="12" t="inlineStr">
+      <c r="D20" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="12" t="inlineStr">
+      <c r="E20" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="12" t="inlineStr">
+      <c r="F20" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 4v4组·RPE=5</t>
-        </is>
-      </c>
-      <c r="H19" s="11" t="inlineStr"/>
-    </row>
-    <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="21" t="inlineStr">
-        <is>
-          <t>中场 (12人·含边前卫1)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n"/>
-      <c r="C20" s="6" t="n"/>
-      <c r="D20" s="6" t="n"/>
-      <c r="E20" s="6" t="n"/>
-      <c r="F20" s="6" t="n"/>
-      <c r="G20" s="6" t="n"/>
-      <c r="H20" s="7" t="n"/>
+      <c r="G20" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·未赴沪</t>
+        </is>
+      </c>
+      <c r="H20" s="31" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>杨翼璇</t>
-        </is>
-      </c>
-      <c r="B21" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="D21" s="12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="F21" s="12" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G21" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=5</t>
-        </is>
-      </c>
-      <c r="H21" s="11" t="inlineStr"/>
+      <c r="A21" s="48" t="inlineStr">
+        <is>
+          <t>中场 11人</t>
+        </is>
+      </c>
+      <c r="B21" s="46" t="n"/>
+      <c r="C21" s="46" t="n"/>
+      <c r="D21" s="46" t="n"/>
+      <c r="E21" s="46" t="n"/>
+      <c r="F21" s="46" t="n"/>
+      <c r="G21" s="46" t="n"/>
+      <c r="H21" s="47" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="18" t="inlineStr">
         <is>
+          <t>杨翼璇</t>
+        </is>
+      </c>
+      <c r="B22" s="21" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="n">
+        <v>23</v>
+      </c>
+      <c r="D22" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E22" s="19" t="n">
+        <v>175</v>
+      </c>
+      <c r="F22" s="19" t="n">
+        <v>68</v>
+      </c>
+      <c r="G22" s="20" t="inlineStr">
+        <is>
+          <t>🟢正常</t>
+        </is>
+      </c>
+      <c r="H22" s="18" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="28" t="inlineStr">
+        <is>
           <t>何麟立</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="F22" s="19" t="inlineStr">
-        <is>
-          <t>68</t>
-        </is>
-      </c>
-      <c r="G22" s="20" t="inlineStr">
-        <is>
-          <t>🟢正常·睡眠5→2✅·腘绳肌已恢复</t>
-        </is>
-      </c>
-      <c r="H22" s="18" t="inlineStr"/>
-    </row>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>55</v>
+      </c>
+      <c r="D23" t="n">
+        <v>26</v>
+      </c>
+      <c r="E23" t="n">
+        <v>175</v>
+      </c>
+      <c r="F23" t="n">
+        <v>68</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5首发全场RPE=10</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="30" t="inlineStr">
         <is>
           <t>布格拉汗-斯坎旦尔</t>
         </is>
       </c>
-      <c r="B23" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C23" s="9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="D23" s="9" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E23" s="9" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F23" s="9" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G23" s="10" t="inlineStr">
-        <is>
-          <t>🔴MCL·⚡D+2·4v4完成✅·变向可控·进度超前</t>
-        </is>
-      </c>
-      <c r="H23" s="8" t="inlineStr">
-        <is>
-          <t>继续康复方案·冰敷·MCL抗外翻</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="B24" s="31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C24" s="31" t="n">
+        <v>10</v>
+      </c>
+      <c r="D24" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E24" s="31" t="n">
+        <v>172</v>
+      </c>
+      <c r="F24" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="G24" s="31" t="inlineStr">
+        <is>
+          <t>🟡MCL恢复中·可替补·8.5替补未登场</t>
+        </is>
+      </c>
+      <c r="H24" s="31" t="inlineStr">
+        <is>
+          <t>跟队合练</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="33" t="inlineStr">
         <is>
           <t>巫林峰</t>
         </is>
       </c>
-      <c r="B24" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C24" s="9" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="D24" s="9" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E24" s="9" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="F24" s="9" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G24" s="10" t="inlineStr">
-        <is>
-          <t>🟢正常·脚掌无新信号·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H24" s="8" t="inlineStr"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="18" t="inlineStr">
+      <c r="B25" s="40" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C25" s="35" t="n">
+        <v>19</v>
+      </c>
+      <c r="D25" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="E25" s="35" t="n">
+        <v>175</v>
+      </c>
+      <c r="F25" s="35" t="n">
+        <v>67</v>
+      </c>
+      <c r="G25" s="39" t="inlineStr">
+        <is>
+          <t>🟢预防维持·8.5首发71'·无新信号</t>
+        </is>
+      </c>
+      <c r="H25" s="35" t="inlineStr"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="30" t="inlineStr">
         <is>
           <t>张辉</t>
         </is>
       </c>
-      <c r="B25" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>176</t>
-        </is>
-      </c>
-      <c r="F25" s="19" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="G25" s="20" t="inlineStr">
-        <is>
-          <t>🟠⚠️ 7/23 RPE=7·肌肉酸·脚腕疼史</t>
-        </is>
-      </c>
-      <c r="H25" s="18" t="inlineStr">
-        <is>
-          <t>10km组·累积疲劳·监控</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+      <c r="B26" s="31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C26" s="31" t="n">
+        <v>38</v>
+      </c>
+      <c r="D26" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E26" s="31" t="n">
+        <v>176</v>
+      </c>
+      <c r="F26" s="31" t="n">
+        <v>69</v>
+      </c>
+      <c r="G26" s="41" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5首发86'</t>
+        </is>
+      </c>
+      <c r="H26" s="31" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="A27" s="33" t="inlineStr">
         <is>
           <t>谢锦政</t>
         </is>
       </c>
-      <c r="B26" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C26" s="12" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="D26" s="12" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E26" s="12" t="inlineStr">
-        <is>
-          <t>174</t>
-        </is>
-      </c>
-      <c r="F26" s="12" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
-      </c>
-      <c r="G26" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·内踝7/22已恢复✅</t>
-        </is>
-      </c>
-      <c r="H26" s="11" t="inlineStr">
-        <is>
-          <t>7/26可全力</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="11" t="inlineStr">
+      <c r="B27" s="40" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C27" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="D27" s="35" t="n">
+        <v>25</v>
+      </c>
+      <c r="E27" s="35" t="n">
+        <v>174</v>
+      </c>
+      <c r="F27" s="35" t="n">
+        <v>66</v>
+      </c>
+      <c r="G27" s="36" t="inlineStr">
+        <is>
+          <t>🔴🆕右脚趾肿·8.8停训</t>
+        </is>
+      </c>
+      <c r="H27" s="35" t="inlineStr">
+        <is>
+          <t>明天大概率缺阵</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="30" t="inlineStr">
         <is>
           <t>栾昊(U21)</t>
         </is>
       </c>
-      <c r="B27" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C27" s="12" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="D27" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E27" s="12" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="F27" s="12" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G27" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H27" s="11" t="inlineStr"/>
-    </row>
-    <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="11" t="inlineStr">
+      <c r="B28" s="31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C28" s="31" t="n">
+        <v>8</v>
+      </c>
+      <c r="D28" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="E28" s="31" t="n">
+        <v>173</v>
+      </c>
+      <c r="F28" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="G28" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常</t>
+        </is>
+      </c>
+      <c r="H28" s="31" t="inlineStr"/>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="33" t="inlineStr">
         <is>
           <t>林楷轩(U21)</t>
         </is>
       </c>
-      <c r="B28" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C28" s="12" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="D28" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="E28" s="12" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F28" s="12" t="inlineStr">
-        <is>
-          <t>64</t>
-        </is>
-      </c>
-      <c r="G28" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·4v4组·酸痛=4(正常反应)</t>
-        </is>
-      </c>
-      <c r="H28" s="11" t="inlineStr"/>
-    </row>
-    <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="11" t="inlineStr">
+      <c r="B29" s="40" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C29" s="35" t="n">
+        <v>27</v>
+      </c>
+      <c r="D29" s="35" t="n">
+        <v>20</v>
+      </c>
+      <c r="E29" s="35" t="n">
+        <v>172</v>
+      </c>
+      <c r="F29" s="35" t="n">
+        <v>64</v>
+      </c>
+      <c r="G29" s="36" t="inlineStr">
+        <is>
+          <t>🟡单独训练·8.8有晨间未参训</t>
+        </is>
+      </c>
+      <c r="H29" s="35" t="inlineStr">
+        <is>
+          <t>体能教练带</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="30" t="inlineStr">
         <is>
           <t>朱云天(U21)</t>
         </is>
       </c>
-      <c r="B29" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C29" s="12" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="D29" s="12" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="E29" s="12" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F29" s="12" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G29" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·4v4组·RPE=4</t>
-        </is>
-      </c>
-      <c r="H29" s="11" t="inlineStr"/>
-    </row>
-    <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="B30" s="31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C30" s="31" t="n">
+        <v>20</v>
+      </c>
+      <c r="D30" s="31" t="n">
+        <v>19</v>
+      </c>
+      <c r="E30" s="31" t="n">
+        <v>172</v>
+      </c>
+      <c r="F30" s="31" t="n">
+        <v>65</v>
+      </c>
+      <c r="G30" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·未赴沪</t>
+        </is>
+      </c>
+      <c r="H30" s="31" t="inlineStr"/>
+    </row>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="33" t="inlineStr">
         <is>
           <t>董德</t>
         </is>
       </c>
-      <c r="B30" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C30" s="12" t="inlineStr">
+      <c r="B31" s="40" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C31" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="12" t="inlineStr">
+      <c r="D31" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E30" s="12" t="inlineStr">
+      <c r="E31" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F30" s="12" t="inlineStr">
+      <c r="F31" s="35" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G30" s="13" t="inlineStr">
-        <is>
-          <t>🟠⚠️ 睡4+RPE=2·投入度待观察</t>
-        </is>
-      </c>
-      <c r="H30" s="11" t="inlineStr">
-        <is>
-          <t>新人·建议沟通</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="14" t="inlineStr">
-        <is>
-          <t>吕佳骏🆕</t>
-        </is>
-      </c>
-      <c r="B31" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
+      <c r="G31" s="42" t="inlineStr">
+        <is>
+          <t>🟢正常·未赴沪</t>
+        </is>
+      </c>
+      <c r="H31" s="35" t="inlineStr"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="30" t="inlineStr">
+        <is>
+          <t>吕佳骏</t>
+        </is>
+      </c>
+      <c r="B32" s="31" t="inlineStr">
+        <is>
+          <t>MID</t>
+        </is>
+      </c>
+      <c r="C32" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="15" t="inlineStr">
+      <c r="D32" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="15" t="inlineStr">
+      <c r="E32" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="15" t="inlineStr">
+      <c r="F32" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="16" t="inlineStr">
-        <is>
-          <t>🟢新人适应·4v4组·10min替换</t>
-        </is>
-      </c>
-      <c r="H31" s="14" t="inlineStr"/>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="14" t="inlineStr">
-        <is>
-          <t>薛悦伟🆕</t>
-        </is>
-      </c>
-      <c r="B32" s="21" t="inlineStr">
-        <is>
-          <t>中场</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="G32" s="16" t="inlineStr">
-        <is>
-          <t>🟠新人·数据全部缺填</t>
-        </is>
-      </c>
-      <c r="H32" s="14" t="inlineStr">
-        <is>
-          <t>提醒补填</t>
-        </is>
-      </c>
+      <c r="G32" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·未赴沪</t>
+        </is>
+      </c>
+      <c r="H32" s="31" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="22" t="inlineStr">
-        <is>
-          <t>前锋 (5人)</t>
-        </is>
-      </c>
-      <c r="B33" s="6" t="n"/>
-      <c r="C33" s="6" t="n"/>
-      <c r="D33" s="6" t="n"/>
-      <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
-      <c r="G33" s="6" t="n"/>
-      <c r="H33" s="7" t="n"/>
+      <c r="A33" s="48" t="inlineStr">
+        <is>
+          <t>前锋 5人</t>
+        </is>
+      </c>
+      <c r="B33" s="46" t="n"/>
+      <c r="C33" s="46" t="n"/>
+      <c r="D33" s="46" t="n"/>
+      <c r="E33" s="46" t="n"/>
+      <c r="F33" s="46" t="n"/>
+      <c r="G33" s="46" t="n"/>
+      <c r="H33" s="47" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="18" t="inlineStr">
+      <c r="A34" s="30" t="inlineStr">
         <is>
           <t>陈祥煜</t>
         </is>
       </c>
-      <c r="B34" s="22" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="C34" s="19" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="D34" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E34" s="19" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
-      <c r="F34" s="19" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="G34" s="20" t="inlineStr">
-        <is>
-          <t>🟢正常·恢复良好✅·7/23 RPE=5</t>
-        </is>
-      </c>
-      <c r="H34" s="18" t="inlineStr"/>
+      <c r="B34" s="31" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C34" s="31" t="n">
+        <v>33</v>
+      </c>
+      <c r="D34" s="31" t="n">
+        <v>25</v>
+      </c>
+      <c r="E34" s="31" t="n">
+        <v>178</v>
+      </c>
+      <c r="F34" s="31" t="n">
+        <v>72</v>
+      </c>
+      <c r="G34" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5首发全场RPE=10</t>
+        </is>
+      </c>
+      <c r="H34" s="31" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="33" t="inlineStr">
         <is>
           <t>艾沙江-库尔班</t>
         </is>
       </c>
-      <c r="B35" s="22" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="C35" s="9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="D35" s="9" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="E35" s="9" t="inlineStr">
-        <is>
-          <t>173</t>
-        </is>
-      </c>
-      <c r="F35" s="9" t="inlineStr">
-        <is>
-          <t>65</t>
-        </is>
-      </c>
-      <c r="G35" s="10" t="inlineStr">
-        <is>
-          <t>🟠左后群紧·持续监控·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H35" s="8" t="inlineStr">
-        <is>
-          <t>训练前激活·赛前三步自测</t>
-        </is>
-      </c>
+      <c r="B35" s="44" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C35" s="35" t="n">
+        <v>7</v>
+      </c>
+      <c r="D35" s="35" t="n">
+        <v>26</v>
+      </c>
+      <c r="E35" s="35" t="n">
+        <v>173</v>
+      </c>
+      <c r="F35" s="35" t="n">
+        <v>65</v>
+      </c>
+      <c r="G35" s="45" t="inlineStr">
+        <is>
+          <t>🟢正常·今日RPE=4</t>
+        </is>
+      </c>
+      <c r="H35" s="35" t="inlineStr"/>
     </row>
     <row r="36" ht="22" customHeight="1">
       <c r="A36" s="18" t="inlineStr">
@@ -2554,148 +2516,149 @@
       </c>
       <c r="B36" s="22" t="inlineStr">
         <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="C36" s="19" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="D36" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E36" s="19" t="inlineStr">
-        <is>
-          <t>172</t>
-        </is>
-      </c>
-      <c r="F36" s="19" t="inlineStr">
-        <is>
-          <t>66</t>
-        </is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" s="19" t="n">
+        <v>25</v>
+      </c>
+      <c r="E36" s="19" t="n">
+        <v>175</v>
+      </c>
+      <c r="F36" s="19" t="n">
+        <v>67</v>
       </c>
       <c r="G36" s="20" t="inlineStr">
         <is>
-          <t>🟠睡眠4→3改善·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H36" s="18" t="inlineStr"/>
+          <t>🟡今日RPE=5·疲3酸3·MD-1负荷偏高</t>
+        </is>
+      </c>
+      <c r="H36" s="18" t="inlineStr">
+        <is>
+          <t>充分恢复</t>
+        </is>
+      </c>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="18" t="inlineStr">
+      <c r="A37" s="28" t="inlineStr">
         <is>
           <t>阿西江-白山</t>
         </is>
       </c>
-      <c r="B37" s="22" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="C37" s="19" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="D37" s="19" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="E37" s="19" t="inlineStr">
-        <is>
-          <t>175</t>
-        </is>
-      </c>
-      <c r="F37" s="19" t="inlineStr">
-        <is>
-          <t>67</t>
-        </is>
-      </c>
-      <c r="G37" s="20" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H37" s="18" t="inlineStr"/>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>14</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>🟡第五趾骨监控·8.5替补未登场</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>持续观察</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="A38" s="30" t="inlineStr">
         <is>
           <t>努尔扎提-努尔兰</t>
         </is>
       </c>
-      <c r="B38" s="22" t="inlineStr">
-        <is>
-          <t>前锋</t>
-        </is>
-      </c>
-      <c r="C38" s="12" t="inlineStr">
+      <c r="B38" s="31" t="inlineStr">
+        <is>
+          <t>FWD</t>
+        </is>
+      </c>
+      <c r="C38" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="12" t="inlineStr">
+      <c r="D38" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="12" t="inlineStr">
+      <c r="E38" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="12" t="inlineStr">
+      <c r="F38" s="31" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="13" t="inlineStr">
-        <is>
-          <t>🟢正常·7/23 RPE=6</t>
-        </is>
-      </c>
-      <c r="H38" s="11" t="inlineStr"/>
+      <c r="G38" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·8.5替补24'</t>
+        </is>
+      </c>
+      <c r="H38" s="31" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="23" t="n"/>
-      <c r="B39" s="23" t="n"/>
-      <c r="C39" s="23" t="n"/>
-      <c r="D39" s="23" t="n"/>
-      <c r="E39" s="23" t="n"/>
-      <c r="F39" s="23" t="n"/>
-      <c r="G39" s="23" t="n"/>
-      <c r="H39" s="23" t="n"/>
+      <c r="A39" s="33" t="n"/>
+      <c r="B39" s="35" t="n"/>
+      <c r="C39" s="35" t="n"/>
+      <c r="D39" s="35" t="n"/>
+      <c r="E39" s="35" t="n"/>
+      <c r="F39" s="35" t="n"/>
+      <c r="G39" s="32" t="n"/>
+      <c r="H39" s="35" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="24" t="inlineStr">
-        <is>
-          <t>31人: 门将4 | 后卫10 | 中场12(含边前卫1) | 前锋5 | 🟢正常18 🟠降量8 🔴康复5 | 7/21更新</t>
-        </is>
-      </c>
+      <c r="A40" s="30" t="n"/>
+      <c r="B40" s="31" t="n"/>
+      <c r="C40" s="31" t="n"/>
+      <c r="D40" s="31" t="n"/>
+      <c r="E40" s="31" t="n"/>
+      <c r="F40" s="31" t="n"/>
+      <c r="G40" s="31" t="n"/>
+      <c r="H40" s="31" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="23" t="n"/>
-      <c r="B41" s="23" t="n"/>
-      <c r="C41" s="23" t="n"/>
-      <c r="D41" s="23" t="n"/>
-      <c r="E41" s="23" t="n"/>
-      <c r="F41" s="23" t="n"/>
-      <c r="G41" s="23" t="n"/>
-      <c r="H41" s="23" t="n"/>
+      <c r="A41" s="33" t="n"/>
+      <c r="B41" s="35" t="n"/>
+      <c r="C41" s="35" t="n"/>
+      <c r="D41" s="35" t="n"/>
+      <c r="E41" s="35" t="n"/>
+      <c r="F41" s="35" t="n"/>
+      <c r="G41" s="41" t="n"/>
+      <c r="H41" s="35" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="23" t="n"/>
-      <c r="B42" s="23" t="n"/>
-      <c r="C42" s="23" t="n"/>
-      <c r="D42" s="23" t="n"/>
-      <c r="E42" s="23" t="n"/>
-      <c r="F42" s="23" t="n"/>
-      <c r="G42" s="23" t="n"/>
-      <c r="H42" s="23" t="n"/>
+      <c r="A42" s="30" t="n"/>
+      <c r="B42" s="31" t="n"/>
+      <c r="C42" s="31" t="n"/>
+      <c r="D42" s="31" t="n"/>
+      <c r="E42" s="31" t="n"/>
+      <c r="F42" s="31" t="n"/>
+      <c r="G42" s="31" t="n"/>
+      <c r="H42" s="31" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="23" t="n"/>
@@ -2778,14 +2741,12 @@
       <c r="H50" s="23" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="7">
-    <mergeCell ref="A9:H9"/>
-    <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A20:H20"/>
+  <mergeCells count="5">
+    <mergeCell ref="A21:H21"/>
     <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A10:H10"/>
     <mergeCell ref="A33:H33"/>
-    <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A40:H40"/>
+    <mergeCell ref="A5:H5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr codeName="ThisWorkbook"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="24460" windowHeight="9700" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="12020" windowHeight="9840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="花名册" sheetId="1" state="visible" r:id="rId1"/>
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="34">
+  <fonts count="30">
     <font>
       <name val="宋体"/>
       <charset val="134"/>
@@ -26,18 +26,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
+      <name val="PingFang SC"/>
       <charset val="134"/>
       <b val="1"/>
       <color rgb="FF992828"/>
       <sz val="14"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
+      <name val="PingFang SC"/>
       <charset val="134"/>
-      <b val="1"/>
-      <color rgb="FF992828"/>
-      <sz val="9"/>
+      <color rgb="FF888888"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
@@ -47,28 +46,40 @@
       <sz val="10"/>
     </font>
     <font>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-      <color rgb="FFCC0000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <charset val="134"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
+      <name val="PingFang SC"/>
       <charset val="134"/>
       <b val="1"/>
-      <color rgb="FF228B22"/>
-      <sz val="10"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="PingFang SC"/>
+      <charset val="134"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
       <b val="1"/>
       <color rgb="FFE67E00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
       <sz val="10"/>
     </font>
     <font>
@@ -222,38 +233,8 @@
       <sz val="11"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <name val="PingFang SC"/>
-      <b val="1"/>
-      <color rgb="00992828"/>
-      <sz val="14"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <color rgb="00888888"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="PingFang SC"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="48">
+  <fills count="47">
     <fill>
       <patternFill/>
     </fill>
@@ -268,60 +249,84 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FF992828"/>
+        <bgColor rgb="FF992828"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF1A1F2E"/>
+        <bgColor rgb="FF1A1F2E"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF5F5F5"/>
+        <bgColor rgb="FFF5F5F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFD9B3"/>
+        <bgColor rgb="FFFFD9B3"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FF555555"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFE8F0E8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2B5797"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFE8D0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF228B22"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor rgb="FFFFC7CE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFE0FFE0"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFCC6600"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFF0E8E8"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFE8F0E8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE0FFE0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF2B5797"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFE8D0"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF228B22"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFCC6600"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE8DCDC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFFFFFCC"/>
         <bgColor indexed="64"/>
       </patternFill>
@@ -504,36 +509,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00992828"/>
-        <bgColor rgb="00992828"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
-        <bgColor rgb="00F5F5F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFD9B3"/>
-        <bgColor rgb="00FFD9B3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
-        <bgColor rgb="00FFC7CE"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="001a1f2e"/>
-        <bgColor rgb="001a1f2e"/>
       </patternFill>
     </fill>
   </fills>
@@ -557,6 +532,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FFCCCCCC"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -686,6 +700,26 @@
       <left/>
       <right/>
       <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
         <color rgb="FFCCCCCC"/>
       </top>
       <bottom/>
@@ -702,65 +736,22 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="12" borderId="4" applyAlignment="1">
+    <xf numFmtId="43" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="10" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="10" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1">
@@ -769,122 +760,131 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="16" borderId="7" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="5" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="6" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="13" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="14" borderId="8" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="14" borderId="7" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="9" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="10" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="11" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="36" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="37" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="38" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="39" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="40" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="41" borderId="0" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="42" borderId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="9" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="11" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="10" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="19" borderId="12" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="13" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="14" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="23" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="24" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="25" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="26" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="27" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="28" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="29" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="30" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="31" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="32" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="33" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="35" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="37" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="39" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="40" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="41" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="42" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="43" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="44" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="45" borderId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="46" borderId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="50">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -898,129 +898,83 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="9" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="11" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="12" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="13" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="14" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="15" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="30" fillId="43" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="44" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="31" fillId="44" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="44" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="45" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="3" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="5" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="7" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="8" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="9" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="46" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="6" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="10" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="32" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="33" fillId="47" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="33" fillId="47" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1473,27 +1427,23 @@
   <dimension ref="A1:H50"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.642857142857141" defaultRowHeight="17.6"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="6" customWidth="1" min="2" max="2"/>
-    <col width="6" customWidth="1" min="3" max="4"/>
-    <col width="6" customWidth="1" min="4" max="4"/>
+    <col width="27.8125" customWidth="1" min="1" max="1"/>
+    <col width="6" customWidth="1" min="2" max="4"/>
     <col width="8" customWidth="1" min="5" max="6"/>
-    <col width="8" customWidth="1" min="6" max="6"/>
-    <col width="40" customWidth="1" min="7" max="7"/>
-    <col width="40" customWidth="1" min="8" max="8"/>
+    <col width="40" customWidth="1" min="7" max="8"/>
   </cols>
   <sheetData>
-    <row r="1" ht="30" customHeight="1">
-      <c r="A1" s="25" t="inlineStr">
+    <row r="1" ht="54" customHeight="1">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>崇德荣海 · 球员花名册 2026</t>
         </is>
       </c>
     </row>
     <row r="2" ht="22" customHeight="1">
-      <c r="A2" s="26" t="inlineStr">
-        <is>
-          <t>30人 · 8/8 · 戚博→海门珂缔缘(租借) · 8/5客1-0海港B · 8/8 MD-1 · 明客vs长春喜都</t>
+      <c r="A2" s="3" t="inlineStr">
+        <is>
+          <t>30人 · 8/9 · ⚽客2-1长春喜都 · 5-4-1 · 帕尔曼江⚽+阿西江⚽ · 戚博→海门租借</t>
         </is>
       </c>
     </row>
@@ -1540,213 +1490,213 @@
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="27" t="inlineStr">
+      <c r="A4" s="5" t="inlineStr">
         <is>
           <t>姓名</t>
         </is>
       </c>
-      <c r="B4" s="27" t="inlineStr">
+      <c r="B4" s="5" t="inlineStr">
         <is>
           <t>位置</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="5" t="inlineStr">
         <is>
           <t>号码</t>
         </is>
       </c>
-      <c r="D4" s="27" t="inlineStr">
+      <c r="D4" s="5" t="inlineStr">
         <is>
           <t>年龄</t>
         </is>
       </c>
-      <c r="E4" s="27" t="inlineStr">
+      <c r="E4" s="5" t="inlineStr">
         <is>
           <t>身高</t>
         </is>
       </c>
-      <c r="F4" s="27" t="inlineStr">
+      <c r="F4" s="5" t="inlineStr">
         <is>
           <t>体重</t>
         </is>
       </c>
-      <c r="G4" s="27" t="inlineStr">
+      <c r="G4" s="5" t="inlineStr">
         <is>
           <t>伤病/状态</t>
         </is>
       </c>
-      <c r="H4" s="27" t="inlineStr">
+      <c r="H4" s="5" t="inlineStr">
         <is>
           <t>备注</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="48" t="inlineStr">
+      <c r="A5" s="6" t="inlineStr">
         <is>
           <t>门将 4人</t>
         </is>
       </c>
-      <c r="B5" s="46" t="n"/>
-      <c r="C5" s="46" t="n"/>
-      <c r="D5" s="46" t="n"/>
-      <c r="E5" s="46" t="n"/>
-      <c r="F5" s="46" t="n"/>
-      <c r="G5" s="46" t="n"/>
-      <c r="H5" s="47" t="n"/>
+      <c r="B5" s="7" t="n"/>
+      <c r="C5" s="7" t="n"/>
+      <c r="D5" s="7" t="n"/>
+      <c r="E5" s="7" t="n"/>
+      <c r="F5" s="7" t="n"/>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="8" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="30" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>张海轩</t>
         </is>
       </c>
-      <c r="B6" s="31" t="inlineStr">
+      <c r="B6" s="10" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="C6" s="31" t="n">
+      <c r="C6" s="10" t="n">
         <v>13</v>
       </c>
-      <c r="D6" s="31" t="n">
+      <c r="D6" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="E6" s="31" t="n">
+      <c r="E6" s="10" t="n">
         <v>185</v>
       </c>
-      <c r="F6" s="31" t="n">
+      <c r="F6" s="10" t="n">
         <v>78</v>
       </c>
-      <c r="G6" s="32" t="inlineStr">
-        <is>
-          <t>🔴脚踝痛D3·今日RPE=4·疲5→2✅·酸4→1✅</t>
-        </is>
-      </c>
-      <c r="H6" s="31" t="inlineStr">
-        <is>
-          <t>赛前评估·可出战</t>
+      <c r="G6" s="11" t="inlineStr">
+        <is>
+          <t>🟡脚踝D4·首发95' RPE=8·扛满全场✅</t>
+        </is>
+      </c>
+      <c r="H6" s="10" t="inlineStr">
+        <is>
+          <t>继续监控</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="33" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
         <is>
           <t>杨卓燠</t>
         </is>
       </c>
-      <c r="B7" s="34" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="C7" s="35" t="n">
+      <c r="C7" s="14" t="n">
         <v>31</v>
       </c>
-      <c r="D7" s="35" t="n">
+      <c r="D7" s="14" t="n">
         <v>24</v>
       </c>
-      <c r="E7" s="35" t="n">
+      <c r="E7" s="14" t="n">
         <v>183</v>
       </c>
-      <c r="F7" s="35" t="n">
+      <c r="F7" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="G7" s="36" t="inlineStr">
-        <is>
-          <t>🟡腰疼D2·今日RPE=3</t>
-        </is>
-      </c>
-      <c r="H7" s="35" t="inlineStr">
+      <c r="G7" s="15" t="inlineStr">
+        <is>
+          <t>🟡腰疼D3·替补未登场</t>
+        </is>
+      </c>
+      <c r="H7" s="14" t="inlineStr">
         <is>
           <t>观察</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="30" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>王款(U21)</t>
         </is>
       </c>
-      <c r="B8" s="31" t="inlineStr">
+      <c r="B8" s="10" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="10" t="n">
         <v>15</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="G8" s="31" t="inlineStr">
+      <c r="G8" s="10" t="inlineStr">
         <is>
           <t>🟢正常</t>
         </is>
       </c>
-      <c r="H8" s="31" t="inlineStr"/>
+      <c r="H8" s="10" t="inlineStr"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="37" t="inlineStr">
+      <c r="A9" s="16" t="inlineStr">
         <is>
           <t>王熙博</t>
         </is>
       </c>
-      <c r="B9" s="35" t="inlineStr">
+      <c r="B9" s="14" t="inlineStr">
         <is>
           <t>GK</t>
         </is>
       </c>
-      <c r="C9" s="35" t="inlineStr">
+      <c r="C9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D9" s="35" t="inlineStr">
+      <c r="D9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="35" t="inlineStr">
+      <c r="E9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F9" s="35" t="inlineStr">
+      <c r="F9" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G9" s="35" t="inlineStr">
+      <c r="G9" s="14" t="inlineStr">
         <is>
           <t>🟢新人适应·未赴沪</t>
         </is>
       </c>
-      <c r="H9" s="35" t="inlineStr"/>
+      <c r="H9" s="14" t="inlineStr"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="49" t="inlineStr">
+      <c r="A10" s="17" t="inlineStr">
         <is>
           <t>后卫 10人</t>
         </is>
       </c>
-      <c r="B10" s="6" t="n"/>
-      <c r="C10" s="6" t="n"/>
-      <c r="D10" s="6" t="n"/>
-      <c r="E10" s="6" t="n"/>
-      <c r="F10" s="6" t="n"/>
-      <c r="G10" s="6" t="n"/>
-      <c r="H10" s="7" t="n"/>
+      <c r="B10" s="18" t="n"/>
+      <c r="C10" s="18" t="n"/>
+      <c r="D10" s="18" t="n"/>
+      <c r="E10" s="18" t="n"/>
+      <c r="F10" s="18" t="n"/>
+      <c r="G10" s="18" t="n"/>
+      <c r="H10" s="19" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="28" t="inlineStr">
+      <c r="A11" s="20" t="inlineStr">
         <is>
           <t>王捷(U21)</t>
         </is>
@@ -1780,335 +1730,339 @@
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="30" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>丁云峰</t>
         </is>
       </c>
-      <c r="B12" s="31" t="inlineStr">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C12" s="31" t="n">
+      <c r="C12" s="10" t="n">
         <v>16</v>
       </c>
-      <c r="D12" s="31" t="n">
+      <c r="D12" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E12" s="31" t="n">
+      <c r="E12" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="F12" s="31" t="n">
+      <c r="F12" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="G12" s="32" t="inlineStr">
-        <is>
-          <t>🟢正常·今日RPE=3</t>
-        </is>
-      </c>
-      <c r="H12" s="31" t="inlineStr"/>
+      <c r="G12" s="11" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=9</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="33" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
         <is>
           <t>凌中阳</t>
         </is>
       </c>
-      <c r="B13" s="38" t="inlineStr">
+      <c r="B13" s="21" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C13" s="35" t="n">
+      <c r="C13" s="14" t="n">
         <v>30</v>
       </c>
-      <c r="D13" s="35" t="n">
+      <c r="D13" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="E13" s="35" t="n">
+      <c r="E13" s="14" t="n">
         <v>182</v>
       </c>
-      <c r="F13" s="35" t="n">
+      <c r="F13" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="G13" s="36" t="inlineStr">
-        <is>
-          <t>🟢正常·今日RPE=3</t>
-        </is>
-      </c>
-      <c r="H13" s="35" t="inlineStr"/>
+      <c r="G13" s="15" t="inlineStr">
+        <is>
+          <t>🟢正常·84'替补11'</t>
+        </is>
+      </c>
+      <c r="H13" s="14" t="inlineStr"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="30" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>陈少豪</t>
         </is>
       </c>
-      <c r="B14" s="31" t="inlineStr">
+      <c r="B14" s="10" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C14" s="31" t="n">
+      <c r="C14" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="D14" s="31" t="n">
+      <c r="D14" s="10" t="n">
         <v>26</v>
       </c>
-      <c r="E14" s="31" t="n">
+      <c r="E14" s="10" t="n">
         <v>181</v>
       </c>
-      <c r="F14" s="31" t="n">
+      <c r="F14" s="10" t="n">
         <v>74</v>
       </c>
-      <c r="G14" s="31" t="inlineStr">
+      <c r="G14" s="10" t="inlineStr">
         <is>
           <t>🟢正常·今日RPE=2</t>
         </is>
       </c>
-      <c r="H14" s="31" t="inlineStr"/>
+      <c r="H14" s="10" t="inlineStr"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="33" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
         <is>
           <t>李金羽</t>
         </is>
       </c>
-      <c r="B15" s="38" t="inlineStr">
+      <c r="B15" s="21" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C15" s="35" t="n">
+      <c r="C15" s="14" t="n">
         <v>22</v>
       </c>
-      <c r="D15" s="35" t="n">
+      <c r="D15" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="E15" s="35" t="n">
+      <c r="E15" s="14" t="n">
         <v>180</v>
       </c>
-      <c r="F15" s="35" t="n">
+      <c r="F15" s="14" t="n">
         <v>73</v>
       </c>
-      <c r="G15" s="39" t="inlineStr">
+      <c r="G15" s="22" t="inlineStr">
         <is>
           <t>🟢正常·今日RPE=2·右膝已恢复✅</t>
         </is>
       </c>
-      <c r="H15" s="35" t="inlineStr"/>
+      <c r="H15" s="14" t="inlineStr"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="30" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>王皓文(U21)</t>
         </is>
       </c>
-      <c r="B16" s="31" t="inlineStr">
+      <c r="B16" s="10" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C16" s="31" t="n">
+      <c r="C16" s="10" t="n">
         <v>24</v>
       </c>
-      <c r="D16" s="31" t="n">
+      <c r="D16" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="E16" s="31" t="n">
+      <c r="E16" s="10" t="n">
         <v>178</v>
       </c>
-      <c r="F16" s="31" t="n">
+      <c r="F16" s="10" t="n">
         <v>70</v>
       </c>
-      <c r="G16" s="31" t="inlineStr">
-        <is>
-          <t>🟢正常·8.5首发全场RPE=9</t>
-        </is>
-      </c>
-      <c r="H16" s="31" t="inlineStr"/>
+      <c r="G16" s="10" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=8</t>
+        </is>
+      </c>
+      <c r="H16" s="10" t="inlineStr"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="33" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
         <is>
           <t>张俊哲</t>
         </is>
       </c>
-      <c r="B17" s="38" t="inlineStr">
+      <c r="B17" s="21" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C17" s="35" t="n">
+      <c r="C17" s="14" t="n">
         <v>60</v>
       </c>
-      <c r="D17" s="35" t="n">
+      <c r="D17" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="E17" s="35" t="n">
+      <c r="E17" s="14" t="n">
         <v>182</v>
       </c>
-      <c r="F17" s="35" t="n">
+      <c r="F17" s="14" t="n">
         <v>75</v>
       </c>
-      <c r="G17" s="36" t="inlineStr">
-        <is>
-          <t>🟢正常·8.5首发92'满分</t>
-        </is>
-      </c>
-      <c r="H17" s="35" t="inlineStr"/>
+      <c r="G17" s="15" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=10满分</t>
+        </is>
+      </c>
+      <c r="H17" s="14" t="inlineStr">
+        <is>
+          <t>D+1泳池恢复</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="30" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>张天龙</t>
         </is>
       </c>
-      <c r="B18" s="31" t="inlineStr">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C18" s="31" t="n">
+      <c r="C18" s="10" t="n">
         <v>39</v>
       </c>
-      <c r="D18" s="31" t="n">
+      <c r="D18" s="10" t="n">
         <v>28</v>
       </c>
-      <c r="E18" s="31" t="n">
+      <c r="E18" s="10" t="n">
         <v>180</v>
       </c>
-      <c r="F18" s="31" t="n">
+      <c r="F18" s="10" t="n">
         <v>73</v>
       </c>
-      <c r="G18" s="31" t="inlineStr">
-        <is>
-          <t>🟢正常·8.5首发全场</t>
-        </is>
-      </c>
-      <c r="H18" s="31" t="inlineStr"/>
+      <c r="G18" s="10" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=8</t>
+        </is>
+      </c>
+      <c r="H18" s="10" t="inlineStr"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="33" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
         <is>
           <t>杨文杰</t>
         </is>
       </c>
-      <c r="B19" s="38" t="inlineStr">
+      <c r="B19" s="21" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C19" s="35" t="n">
+      <c r="C19" s="14" t="n">
         <v>5</v>
       </c>
-      <c r="D19" s="35" t="inlineStr">
+      <c r="D19" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E19" s="35" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F19" s="35" t="inlineStr">
+      <c r="F19" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G19" s="36" t="inlineStr">
+      <c r="G19" s="15" t="inlineStr">
         <is>
           <t>🟢正常</t>
         </is>
       </c>
-      <c r="H19" s="35" t="inlineStr"/>
+      <c r="H19" s="14" t="inlineStr"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="30" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>刘子洁</t>
         </is>
       </c>
-      <c r="B20" s="31" t="inlineStr">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>DEF</t>
         </is>
       </c>
-      <c r="C20" s="31" t="inlineStr">
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D20" s="31" t="inlineStr">
+      <c r="D20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E20" s="31" t="inlineStr">
+      <c r="E20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F20" s="31" t="inlineStr">
+      <c r="F20" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G20" s="31" t="inlineStr">
+      <c r="G20" s="10" t="inlineStr">
         <is>
           <t>🟢正常·未赴沪</t>
         </is>
       </c>
-      <c r="H20" s="31" t="inlineStr"/>
+      <c r="H20" s="10" t="inlineStr"/>
     </row>
     <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="48" t="inlineStr">
+      <c r="A21" s="6" t="inlineStr">
         <is>
           <t>中场 11人</t>
         </is>
       </c>
-      <c r="B21" s="46" t="n"/>
-      <c r="C21" s="46" t="n"/>
-      <c r="D21" s="46" t="n"/>
-      <c r="E21" s="46" t="n"/>
-      <c r="F21" s="46" t="n"/>
-      <c r="G21" s="46" t="n"/>
-      <c r="H21" s="47" t="n"/>
+      <c r="B21" s="7" t="n"/>
+      <c r="C21" s="7" t="n"/>
+      <c r="D21" s="7" t="n"/>
+      <c r="E21" s="7" t="n"/>
+      <c r="F21" s="7" t="n"/>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="8" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="18" t="inlineStr">
+      <c r="A22" s="23" t="inlineStr">
         <is>
           <t>杨翼璇</t>
         </is>
       </c>
-      <c r="B22" s="21" t="inlineStr">
+      <c r="B22" s="24" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C22" s="19" t="n">
+      <c r="C22" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="D22" s="19" t="n">
+      <c r="D22" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="E22" s="19" t="n">
+      <c r="E22" s="25" t="n">
         <v>175</v>
       </c>
-      <c r="F22" s="19" t="n">
+      <c r="F22" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="G22" s="20" t="inlineStr">
+      <c r="G22" s="26" t="inlineStr">
         <is>
           <t>🟢正常</t>
         </is>
       </c>
-      <c r="H22" s="18" t="inlineStr"/>
+      <c r="H22" s="23" t="inlineStr"/>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="28" t="inlineStr">
+      <c r="A23" s="20" t="inlineStr">
         <is>
           <t>何麟立</t>
         </is>
@@ -2132,418 +2086,419 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🟢正常·8.5首发全场RPE=10</t>
-        </is>
-      </c>
+          <t>🟢正常·首发84' RPE=8</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="30" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>布格拉汗-斯坎旦尔</t>
         </is>
       </c>
-      <c r="B24" s="31" t="inlineStr">
+      <c r="B24" s="10" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C24" s="31" t="n">
+      <c r="C24" s="10" t="n">
         <v>10</v>
       </c>
-      <c r="D24" s="31" t="n">
+      <c r="D24" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E24" s="31" t="n">
+      <c r="E24" s="10" t="n">
         <v>172</v>
       </c>
-      <c r="F24" s="31" t="n">
+      <c r="F24" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="G24" s="31" t="inlineStr">
+      <c r="G24" s="10" t="inlineStr">
         <is>
           <t>🟡MCL恢复中·可替补·8.5替补未登场</t>
         </is>
       </c>
-      <c r="H24" s="31" t="inlineStr">
+      <c r="H24" s="10" t="inlineStr">
         <is>
           <t>跟队合练</t>
         </is>
       </c>
     </row>
     <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="33" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
         <is>
           <t>巫林峰</t>
         </is>
       </c>
-      <c r="B25" s="40" t="inlineStr">
+      <c r="B25" s="27" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C25" s="35" t="n">
+      <c r="C25" s="14" t="n">
         <v>19</v>
       </c>
-      <c r="D25" s="35" t="n">
+      <c r="D25" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="E25" s="35" t="n">
+      <c r="E25" s="14" t="n">
         <v>175</v>
       </c>
-      <c r="F25" s="35" t="n">
+      <c r="F25" s="14" t="n">
         <v>67</v>
       </c>
-      <c r="G25" s="39" t="inlineStr">
-        <is>
-          <t>🟢预防维持·8.5首发71'·无新信号</t>
-        </is>
-      </c>
-      <c r="H25" s="35" t="inlineStr"/>
+      <c r="G25" s="22" t="inlineStr">
+        <is>
+          <t>🟢正常·首发55' RPE=8</t>
+        </is>
+      </c>
+      <c r="H25" s="14" t="inlineStr"/>
     </row>
     <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="30" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>张辉</t>
         </is>
       </c>
-      <c r="B26" s="31" t="inlineStr">
+      <c r="B26" s="10" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C26" s="31" t="n">
+      <c r="C26" s="10" t="n">
         <v>38</v>
       </c>
-      <c r="D26" s="31" t="n">
+      <c r="D26" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E26" s="31" t="n">
+      <c r="E26" s="10" t="n">
         <v>176</v>
       </c>
-      <c r="F26" s="31" t="n">
+      <c r="F26" s="10" t="n">
         <v>69</v>
       </c>
-      <c r="G26" s="41" t="inlineStr">
-        <is>
-          <t>🟢正常·8.5首发86'</t>
-        </is>
-      </c>
-      <c r="H26" s="31" t="inlineStr"/>
+      <c r="G26" s="28" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=8</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr"/>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="33" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
         <is>
           <t>谢锦政</t>
         </is>
       </c>
-      <c r="B27" s="40" t="inlineStr">
+      <c r="B27" s="27" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C27" s="35" t="n">
+      <c r="C27" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="D27" s="35" t="n">
+      <c r="D27" s="14" t="n">
         <v>25</v>
       </c>
-      <c r="E27" s="35" t="n">
+      <c r="E27" s="14" t="n">
         <v>174</v>
       </c>
-      <c r="F27" s="35" t="n">
+      <c r="F27" s="14" t="n">
         <v>66</v>
       </c>
-      <c r="G27" s="36" t="inlineStr">
-        <is>
-          <t>🔴🆕右脚趾肿·8.8停训</t>
-        </is>
-      </c>
-      <c r="H27" s="35" t="inlineStr">
-        <is>
-          <t>明天大概率缺阵</t>
+      <c r="G27" s="15" t="inlineStr">
+        <is>
+          <t>🔴脚趾肿·未进名单D2</t>
+        </is>
+      </c>
+      <c r="H27" s="14" t="inlineStr">
+        <is>
+          <t>继续观察</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="30" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>栾昊(U21)</t>
         </is>
       </c>
-      <c r="B28" s="31" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C28" s="31" t="n">
+      <c r="C28" s="10" t="n">
         <v>8</v>
       </c>
-      <c r="D28" s="31" t="n">
+      <c r="D28" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="E28" s="31" t="n">
+      <c r="E28" s="10" t="n">
         <v>173</v>
       </c>
-      <c r="F28" s="31" t="n">
+      <c r="F28" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="G28" s="31" t="inlineStr">
+      <c r="G28" s="10" t="inlineStr">
         <is>
           <t>🟢正常</t>
         </is>
       </c>
-      <c r="H28" s="31" t="inlineStr"/>
+      <c r="H28" s="10" t="inlineStr"/>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="33" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
         <is>
           <t>林楷轩(U21)</t>
         </is>
       </c>
-      <c r="B29" s="40" t="inlineStr">
+      <c r="B29" s="27" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C29" s="35" t="n">
+      <c r="C29" s="14" t="n">
         <v>27</v>
       </c>
-      <c r="D29" s="35" t="n">
+      <c r="D29" s="14" t="n">
         <v>20</v>
       </c>
-      <c r="E29" s="35" t="n">
+      <c r="E29" s="14" t="n">
         <v>172</v>
       </c>
-      <c r="F29" s="35" t="n">
+      <c r="F29" s="14" t="n">
         <v>64</v>
       </c>
-      <c r="G29" s="36" t="inlineStr">
-        <is>
-          <t>🟡单独训练·8.8有晨间未参训</t>
-        </is>
-      </c>
-      <c r="H29" s="35" t="inlineStr">
+      <c r="G29" s="15" t="inlineStr">
+        <is>
+          <t>🟡单独训练·未进名单</t>
+        </is>
+      </c>
+      <c r="H29" s="14" t="inlineStr">
         <is>
           <t>体能教练带</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="30" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>朱云天(U21)</t>
         </is>
       </c>
-      <c r="B30" s="31" t="inlineStr">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C30" s="31" t="n">
+      <c r="C30" s="10" t="n">
         <v>20</v>
       </c>
-      <c r="D30" s="31" t="n">
+      <c r="D30" s="10" t="n">
         <v>19</v>
       </c>
-      <c r="E30" s="31" t="n">
+      <c r="E30" s="10" t="n">
         <v>172</v>
       </c>
-      <c r="F30" s="31" t="n">
+      <c r="F30" s="10" t="n">
         <v>65</v>
       </c>
-      <c r="G30" s="31" t="inlineStr">
+      <c r="G30" s="10" t="inlineStr">
         <is>
           <t>🟢正常·未赴沪</t>
         </is>
       </c>
-      <c r="H30" s="31" t="inlineStr"/>
+      <c r="H30" s="10" t="inlineStr"/>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="33" t="inlineStr">
+      <c r="A31" s="12" t="inlineStr">
         <is>
           <t>董德</t>
         </is>
       </c>
-      <c r="B31" s="40" t="inlineStr">
+      <c r="B31" s="27" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C31" s="35" t="inlineStr">
+      <c r="C31" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D31" s="35" t="inlineStr">
+      <c r="D31" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E31" s="35" t="inlineStr">
+      <c r="E31" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F31" s="35" t="inlineStr">
+      <c r="F31" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G31" s="42" t="inlineStr">
+      <c r="G31" s="29" t="inlineStr">
         <is>
           <t>🟢正常·未赴沪</t>
         </is>
       </c>
-      <c r="H31" s="35" t="inlineStr"/>
+      <c r="H31" s="14" t="inlineStr"/>
     </row>
     <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="30" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>吕佳骏</t>
         </is>
       </c>
-      <c r="B32" s="31" t="inlineStr">
+      <c r="B32" s="10" t="inlineStr">
         <is>
           <t>MID</t>
         </is>
       </c>
-      <c r="C32" s="31" t="inlineStr">
+      <c r="C32" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D32" s="31" t="inlineStr">
+      <c r="D32" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E32" s="31" t="inlineStr">
+      <c r="E32" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F32" s="31" t="inlineStr">
+      <c r="F32" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G32" s="31" t="inlineStr">
+      <c r="G32" s="10" t="inlineStr">
         <is>
           <t>🟢正常·未赴沪</t>
         </is>
       </c>
-      <c r="H32" s="31" t="inlineStr"/>
+      <c r="H32" s="10" t="inlineStr"/>
     </row>
     <row r="33">
-      <c r="A33" s="48" t="inlineStr">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>前锋 5人</t>
         </is>
       </c>
-      <c r="B33" s="46" t="n"/>
-      <c r="C33" s="46" t="n"/>
-      <c r="D33" s="46" t="n"/>
-      <c r="E33" s="46" t="n"/>
-      <c r="F33" s="46" t="n"/>
-      <c r="G33" s="46" t="n"/>
-      <c r="H33" s="47" t="n"/>
+      <c r="B33" s="7" t="n"/>
+      <c r="C33" s="7" t="n"/>
+      <c r="D33" s="7" t="n"/>
+      <c r="E33" s="7" t="n"/>
+      <c r="F33" s="7" t="n"/>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="8" t="n"/>
     </row>
     <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="30" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>陈祥煜</t>
         </is>
       </c>
-      <c r="B34" s="31" t="inlineStr">
+      <c r="B34" s="10" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="C34" s="31" t="n">
+      <c r="C34" s="10" t="n">
         <v>33</v>
       </c>
-      <c r="D34" s="31" t="n">
+      <c r="D34" s="10" t="n">
         <v>25</v>
       </c>
-      <c r="E34" s="31" t="n">
+      <c r="E34" s="10" t="n">
         <v>178</v>
       </c>
-      <c r="F34" s="31" t="n">
+      <c r="F34" s="10" t="n">
         <v>72</v>
       </c>
-      <c r="G34" s="31" t="inlineStr">
-        <is>
-          <t>🟢正常·8.5首发全场RPE=10</t>
-        </is>
-      </c>
-      <c r="H34" s="31" t="inlineStr"/>
+      <c r="G34" s="10" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=9</t>
+        </is>
+      </c>
+      <c r="H34" s="10" t="inlineStr"/>
     </row>
     <row r="35" ht="22" customHeight="1">
-      <c r="A35" s="33" t="inlineStr">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>艾沙江-库尔班</t>
         </is>
       </c>
-      <c r="B35" s="44" t="inlineStr">
+      <c r="B35" s="30" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="C35" s="35" t="n">
+      <c r="C35" s="14" t="n">
         <v>7</v>
       </c>
-      <c r="D35" s="35" t="n">
+      <c r="D35" s="14" t="n">
         <v>26</v>
       </c>
-      <c r="E35" s="35" t="n">
+      <c r="E35" s="14" t="n">
         <v>173</v>
       </c>
-      <c r="F35" s="35" t="n">
+      <c r="F35" s="14" t="n">
         <v>65</v>
       </c>
-      <c r="G35" s="45" t="inlineStr">
-        <is>
-          <t>🟢正常·今日RPE=4</t>
-        </is>
-      </c>
-      <c r="H35" s="35" t="inlineStr"/>
+      <c r="G35" s="31" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' RPE=10</t>
+        </is>
+      </c>
+      <c r="H35" s="14" t="inlineStr">
+        <is>
+          <t>D+1恢复</t>
+        </is>
+      </c>
     </row>
     <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="18" t="inlineStr">
+      <c r="A36" s="23" t="inlineStr">
         <is>
           <t>帕尔曼江-克尤木</t>
         </is>
       </c>
-      <c r="B36" s="22" t="inlineStr">
+      <c r="B36" s="32" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="D36" s="19" t="n">
+      <c r="D36" s="25" t="n">
         <v>25</v>
       </c>
-      <c r="E36" s="19" t="n">
+      <c r="E36" s="25" t="n">
         <v>175</v>
       </c>
-      <c r="F36" s="19" t="n">
+      <c r="F36" s="25" t="n">
         <v>67</v>
       </c>
-      <c r="G36" s="20" t="inlineStr">
-        <is>
-          <t>🟡今日RPE=5·疲3酸3·MD-1负荷偏高</t>
-        </is>
-      </c>
-      <c r="H36" s="18" t="inlineStr">
-        <is>
-          <t>充分恢复</t>
-        </is>
-      </c>
+      <c r="G36" s="26" t="inlineStr">
+        <is>
+          <t>🟢正常·首发95' ⚽进球 RPE=9</t>
+        </is>
+      </c>
+      <c r="H36" s="23" t="inlineStr"/>
     </row>
     <row r="37" ht="22" customHeight="1">
-      <c r="A37" s="28" t="inlineStr">
+      <c r="A37" s="20" t="inlineStr">
         <is>
           <t>阿西江-白山</t>
         </is>
@@ -2573,172 +2528,168 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>🟡第五趾骨监控·8.5替补未登场</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>持续观察</t>
-        </is>
-      </c>
+          <t>🟢正常·55'替补登场 ⚽进球·趾骨已恢复✅</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
-      <c r="A38" s="30" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>努尔扎提-努尔兰</t>
         </is>
       </c>
-      <c r="B38" s="31" t="inlineStr">
+      <c r="B38" s="10" t="inlineStr">
         <is>
           <t>FWD</t>
         </is>
       </c>
-      <c r="C38" s="31" t="inlineStr">
+      <c r="C38" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="D38" s="31" t="inlineStr">
+      <c r="D38" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E38" s="31" t="inlineStr">
+      <c r="E38" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F38" s="31" t="inlineStr">
+      <c r="F38" s="10" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G38" s="31" t="inlineStr">
+      <c r="G38" s="10" t="inlineStr">
         <is>
           <t>🟢正常·8.5替补24'</t>
         </is>
       </c>
-      <c r="H38" s="31" t="inlineStr"/>
+      <c r="H38" s="10" t="inlineStr"/>
     </row>
     <row r="39">
-      <c r="A39" s="33" t="n"/>
-      <c r="B39" s="35" t="n"/>
-      <c r="C39" s="35" t="n"/>
-      <c r="D39" s="35" t="n"/>
-      <c r="E39" s="35" t="n"/>
-      <c r="F39" s="35" t="n"/>
-      <c r="G39" s="32" t="n"/>
-      <c r="H39" s="35" t="n"/>
+      <c r="A39" s="12" t="n"/>
+      <c r="B39" s="14" t="n"/>
+      <c r="C39" s="14" t="n"/>
+      <c r="D39" s="14" t="n"/>
+      <c r="E39" s="14" t="n"/>
+      <c r="F39" s="14" t="n"/>
+      <c r="G39" s="11" t="n"/>
+      <c r="H39" s="14" t="n"/>
     </row>
     <row r="40">
-      <c r="A40" s="30" t="n"/>
-      <c r="B40" s="31" t="n"/>
-      <c r="C40" s="31" t="n"/>
-      <c r="D40" s="31" t="n"/>
-      <c r="E40" s="31" t="n"/>
-      <c r="F40" s="31" t="n"/>
-      <c r="G40" s="31" t="n"/>
-      <c r="H40" s="31" t="n"/>
+      <c r="A40" s="9" t="n"/>
+      <c r="B40" s="10" t="n"/>
+      <c r="C40" s="10" t="n"/>
+      <c r="D40" s="10" t="n"/>
+      <c r="E40" s="10" t="n"/>
+      <c r="F40" s="10" t="n"/>
+      <c r="G40" s="10" t="n"/>
+      <c r="H40" s="10" t="n"/>
     </row>
     <row r="41">
-      <c r="A41" s="33" t="n"/>
-      <c r="B41" s="35" t="n"/>
-      <c r="C41" s="35" t="n"/>
-      <c r="D41" s="35" t="n"/>
-      <c r="E41" s="35" t="n"/>
-      <c r="F41" s="35" t="n"/>
-      <c r="G41" s="41" t="n"/>
-      <c r="H41" s="35" t="n"/>
+      <c r="A41" s="12" t="n"/>
+      <c r="B41" s="14" t="n"/>
+      <c r="C41" s="14" t="n"/>
+      <c r="D41" s="14" t="n"/>
+      <c r="E41" s="14" t="n"/>
+      <c r="F41" s="14" t="n"/>
+      <c r="G41" s="28" t="n"/>
+      <c r="H41" s="14" t="n"/>
     </row>
     <row r="42">
-      <c r="A42" s="30" t="n"/>
-      <c r="B42" s="31" t="n"/>
-      <c r="C42" s="31" t="n"/>
-      <c r="D42" s="31" t="n"/>
-      <c r="E42" s="31" t="n"/>
-      <c r="F42" s="31" t="n"/>
-      <c r="G42" s="31" t="n"/>
-      <c r="H42" s="31" t="n"/>
+      <c r="A42" s="9" t="n"/>
+      <c r="B42" s="10" t="n"/>
+      <c r="C42" s="10" t="n"/>
+      <c r="D42" s="10" t="n"/>
+      <c r="E42" s="10" t="n"/>
+      <c r="F42" s="10" t="n"/>
+      <c r="G42" s="10" t="n"/>
+      <c r="H42" s="10" t="n"/>
     </row>
     <row r="43">
-      <c r="A43" s="23" t="n"/>
-      <c r="B43" s="23" t="n"/>
-      <c r="C43" s="23" t="n"/>
-      <c r="D43" s="23" t="n"/>
-      <c r="E43" s="23" t="n"/>
-      <c r="F43" s="23" t="n"/>
-      <c r="G43" s="23" t="n"/>
-      <c r="H43" s="23" t="n"/>
+      <c r="A43" s="33" t="n"/>
+      <c r="B43" s="33" t="n"/>
+      <c r="C43" s="33" t="n"/>
+      <c r="D43" s="33" t="n"/>
+      <c r="E43" s="33" t="n"/>
+      <c r="F43" s="33" t="n"/>
+      <c r="G43" s="33" t="n"/>
+      <c r="H43" s="33" t="n"/>
     </row>
     <row r="44">
-      <c r="A44" s="23" t="n"/>
-      <c r="B44" s="23" t="n"/>
-      <c r="C44" s="23" t="n"/>
-      <c r="D44" s="23" t="n"/>
-      <c r="E44" s="23" t="n"/>
-      <c r="F44" s="23" t="n"/>
-      <c r="G44" s="23" t="n"/>
-      <c r="H44" s="23" t="n"/>
+      <c r="A44" s="33" t="n"/>
+      <c r="B44" s="33" t="n"/>
+      <c r="C44" s="33" t="n"/>
+      <c r="D44" s="33" t="n"/>
+      <c r="E44" s="33" t="n"/>
+      <c r="F44" s="33" t="n"/>
+      <c r="G44" s="33" t="n"/>
+      <c r="H44" s="33" t="n"/>
     </row>
     <row r="45">
-      <c r="A45" s="23" t="n"/>
-      <c r="B45" s="23" t="n"/>
-      <c r="C45" s="23" t="n"/>
-      <c r="D45" s="23" t="n"/>
-      <c r="E45" s="23" t="n"/>
-      <c r="F45" s="23" t="n"/>
-      <c r="G45" s="23" t="n"/>
-      <c r="H45" s="23" t="n"/>
+      <c r="A45" s="33" t="n"/>
+      <c r="B45" s="33" t="n"/>
+      <c r="C45" s="33" t="n"/>
+      <c r="D45" s="33" t="n"/>
+      <c r="E45" s="33" t="n"/>
+      <c r="F45" s="33" t="n"/>
+      <c r="G45" s="33" t="n"/>
+      <c r="H45" s="33" t="n"/>
     </row>
     <row r="46">
-      <c r="A46" s="23" t="n"/>
-      <c r="B46" s="23" t="n"/>
-      <c r="C46" s="23" t="n"/>
-      <c r="D46" s="23" t="n"/>
-      <c r="E46" s="23" t="n"/>
-      <c r="F46" s="23" t="n"/>
-      <c r="G46" s="23" t="n"/>
-      <c r="H46" s="23" t="n"/>
+      <c r="A46" s="33" t="n"/>
+      <c r="B46" s="33" t="n"/>
+      <c r="C46" s="33" t="n"/>
+      <c r="D46" s="33" t="n"/>
+      <c r="E46" s="33" t="n"/>
+      <c r="F46" s="33" t="n"/>
+      <c r="G46" s="33" t="n"/>
+      <c r="H46" s="33" t="n"/>
     </row>
     <row r="47">
-      <c r="A47" s="23" t="n"/>
-      <c r="B47" s="23" t="n"/>
-      <c r="C47" s="23" t="n"/>
-      <c r="D47" s="23" t="n"/>
-      <c r="E47" s="23" t="n"/>
-      <c r="F47" s="23" t="n"/>
-      <c r="G47" s="23" t="n"/>
-      <c r="H47" s="23" t="n"/>
+      <c r="A47" s="33" t="n"/>
+      <c r="B47" s="33" t="n"/>
+      <c r="C47" s="33" t="n"/>
+      <c r="D47" s="33" t="n"/>
+      <c r="E47" s="33" t="n"/>
+      <c r="F47" s="33" t="n"/>
+      <c r="G47" s="33" t="n"/>
+      <c r="H47" s="33" t="n"/>
     </row>
     <row r="48">
-      <c r="A48" s="23" t="n"/>
-      <c r="B48" s="23" t="n"/>
-      <c r="C48" s="23" t="n"/>
-      <c r="D48" s="23" t="n"/>
-      <c r="E48" s="23" t="n"/>
-      <c r="F48" s="23" t="n"/>
-      <c r="G48" s="23" t="n"/>
-      <c r="H48" s="23" t="n"/>
+      <c r="A48" s="33" t="n"/>
+      <c r="B48" s="33" t="n"/>
+      <c r="C48" s="33" t="n"/>
+      <c r="D48" s="33" t="n"/>
+      <c r="E48" s="33" t="n"/>
+      <c r="F48" s="33" t="n"/>
+      <c r="G48" s="33" t="n"/>
+      <c r="H48" s="33" t="n"/>
     </row>
     <row r="49">
-      <c r="A49" s="23" t="n"/>
-      <c r="B49" s="23" t="n"/>
-      <c r="C49" s="23" t="n"/>
-      <c r="D49" s="23" t="n"/>
-      <c r="E49" s="23" t="n"/>
-      <c r="F49" s="23" t="n"/>
-      <c r="G49" s="23" t="n"/>
-      <c r="H49" s="23" t="n"/>
+      <c r="A49" s="33" t="n"/>
+      <c r="B49" s="33" t="n"/>
+      <c r="C49" s="33" t="n"/>
+      <c r="D49" s="33" t="n"/>
+      <c r="E49" s="33" t="n"/>
+      <c r="F49" s="33" t="n"/>
+      <c r="G49" s="33" t="n"/>
+      <c r="H49" s="33" t="n"/>
     </row>
     <row r="50">
-      <c r="A50" s="23" t="n"/>
-      <c r="B50" s="23" t="n"/>
-      <c r="C50" s="23" t="n"/>
-      <c r="D50" s="23" t="n"/>
-      <c r="E50" s="23" t="n"/>
-      <c r="F50" s="23" t="n"/>
-      <c r="G50" s="23" t="n"/>
-      <c r="H50" s="23" t="n"/>
+      <c r="A50" s="33" t="n"/>
+      <c r="B50" s="33" t="n"/>
+      <c r="C50" s="33" t="n"/>
+      <c r="D50" s="33" t="n"/>
+      <c r="E50" s="33" t="n"/>
+      <c r="F50" s="33" t="n"/>
+      <c r="G50" s="33" t="n"/>
+      <c r="H50" s="33" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="5">

--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -2089,7 +2089,6 @@
           <t>🟢正常·首发84' RPE=8</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
     </row>
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="9" t="inlineStr">
@@ -2458,12 +2457,12 @@
       </c>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=10</t>
+          <t>🔴赛前MCL疼·仍首发95' RPE=10·需密切观察</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>D+1恢复</t>
+          <t>D+1评估·减负荷</t>
         </is>
       </c>
     </row>
@@ -2531,7 +2530,6 @@
           <t>🟢正常·55'替补登场 ⚽进球·趾骨已恢复✅</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
     </row>
     <row r="38" ht="22" customHeight="1">
       <c r="A38" s="9" t="inlineStr">

--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -1443,7 +1443,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>30人 · 8/9 · ⚽客2-1长春喜都 · 5-4-1 · 帕尔曼江⚽+阿西江⚽ · 戚博→海门租借</t>
+          <t>30人 · 8/11 · D+2恢复 · 8/15客vs青岛红狮</t>
         </is>
       </c>
     </row>
@@ -1570,12 +1570,12 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>🟡脚踝D4·首发95' RPE=8·扛满全场✅</t>
+          <t>🟡脚踝D6·疲3酸3</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
         <is>
-          <t>继续监控</t>
+          <t>继续冰敷踝泵</t>
         </is>
       </c>
     </row>
@@ -1754,10 +1754,14 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=9</t>
-        </is>
-      </c>
-      <c r="H12" s="10" t="inlineStr"/>
+          <t>🟡左腿后群反应🆕·D+2课后报告</t>
+        </is>
+      </c>
+      <c r="H12" s="10" t="inlineStr">
+        <is>
+          <t>D+3观察减量</t>
+        </is>
+      </c>
     </row>
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="12" t="inlineStr">
@@ -2086,7 +2090,12 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🟢正常·首发84' RPE=8</t>
+          <t>🟡内收肌紧·疲3酸3</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>泡沫轴+拉伸</t>
         </is>
       </c>
     </row>
@@ -2179,10 +2188,14 @@
       </c>
       <c r="G26" s="28" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=8</t>
-        </is>
-      </c>
-      <c r="H26" s="10" t="inlineStr"/>
+          <t>🟡脚腕微痛🆕·仍参训RPE=2</t>
+        </is>
+      </c>
+      <c r="H26" s="10" t="inlineStr">
+        <is>
+          <t>观察</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="12" t="inlineStr">
@@ -2457,12 +2470,12 @@
       </c>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>🔴赛前MCL疼·仍首发95' RPE=10·需密切观察</t>
+          <t>🔴赛前MCL疼·D+2 RPE=5偏高⚠️</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
         <is>
-          <t>D+1评估·减负荷</t>
+          <t>D+3降负荷</t>
         </is>
       </c>
     </row>

--- a/public/share/data/球员档案.xlsx
+++ b/public/share/data/球员档案.xlsx
@@ -1443,7 +1443,7 @@
     <row r="2" ht="22" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>30人 · 8/11 · D+2恢复 · 8/15客vs青岛红狮</t>
+          <t>30人 · 8/13 · MD-2 · 8/15客vs青岛红狮</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="G6" s="11" t="inlineStr">
         <is>
-          <t>🟡脚踝D6·疲3酸3</t>
+          <t>🔴脚踝D7·8/13缺席·8/15出战存疑</t>
         </is>
       </c>
       <c r="H6" s="10" t="inlineStr">
@@ -1604,7 +1604,7 @@
       </c>
       <c r="G7" s="15" t="inlineStr">
         <is>
-          <t>🟡腰疼D3·替补未登场</t>
+          <t>🟢正常（腰疼已恢复）</t>
         </is>
       </c>
       <c r="H7" s="14" t="inlineStr">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="G9" s="14" t="inlineStr">
         <is>
-          <t>🟢新人适应·未赴沪</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H9" s="14" t="inlineStr"/>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>🟡左膝髌腱炎·今日RPE=2·疲3</t>
+          <t>🟡左膝髌腱炎·等长维持</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1754,7 +1754,7 @@
       </c>
       <c r="G12" s="11" t="inlineStr">
         <is>
-          <t>🟡左腿后群反应🆕·D+2课后报告</t>
+          <t>🟢已恢复（左腿后群）</t>
         </is>
       </c>
       <c r="H12" s="10" t="inlineStr">
@@ -1788,7 +1788,7 @@
       </c>
       <c r="G13" s="15" t="inlineStr">
         <is>
-          <t>🟢正常·84'替补11'</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H13" s="14" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="G14" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·今日RPE=2</t>
+          <t>🟢正常·8/13单练</t>
         </is>
       </c>
       <c r="H14" s="10" t="inlineStr"/>
@@ -1848,7 +1848,7 @@
       </c>
       <c r="G15" s="22" t="inlineStr">
         <is>
-          <t>🟢正常·今日RPE=2·右膝已恢复✅</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H15" s="14" t="inlineStr"/>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="G16" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=8</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H16" s="10" t="inlineStr"/>
@@ -1908,7 +1908,7 @@
       </c>
       <c r="G17" s="15" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=10满分</t>
+          <t>🟡脚微痛🆕</t>
         </is>
       </c>
       <c r="H17" s="14" t="inlineStr">
@@ -1942,7 +1942,7 @@
       </c>
       <c r="G18" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=8</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H18" s="10" t="inlineStr"/>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="G19" s="15" t="inlineStr">
         <is>
-          <t>🟢正常</t>
+          <t>🟢正常·8/13单练</t>
         </is>
       </c>
       <c r="H19" s="14" t="inlineStr"/>
@@ -2016,7 +2016,7 @@
       </c>
       <c r="G20" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·未赴沪</t>
+          <t>🟢正常·8/13参训</t>
         </is>
       </c>
       <c r="H20" s="10" t="inlineStr"/>
@@ -2090,7 +2090,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>🟡内收肌紧·疲3酸3</t>
+          <t>🟢已恢复（内收肌）</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="G24" s="10" t="inlineStr">
         <is>
-          <t>🟡MCL恢复中·可替补·8.5替补未登场</t>
+          <t>🟡MCL恢复中·8/13参训</t>
         </is>
       </c>
       <c r="H24" s="10" t="inlineStr">
@@ -2158,7 +2158,7 @@
       </c>
       <c r="G25" s="22" t="inlineStr">
         <is>
-          <t>🟢正常·首发55' RPE=8</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H25" s="14" t="inlineStr"/>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="G26" s="28" t="inlineStr">
         <is>
-          <t>🟡脚腕微痛🆕·仍参训RPE=2</t>
+          <t>🟡黄牌停赛·8/15不上</t>
         </is>
       </c>
       <c r="H26" s="10" t="inlineStr">
@@ -2222,7 +2222,7 @@
       </c>
       <c r="G27" s="15" t="inlineStr">
         <is>
-          <t>🔴脚趾肿·未进名单D2</t>
+          <t>🟢已恢复（脚趾）·8/15未跟队</t>
         </is>
       </c>
       <c r="H27" s="14" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="G28" s="10" t="inlineStr">
         <is>
-          <t>🟢正常</t>
+          <t>🟢正常·8/13单练</t>
         </is>
       </c>
       <c r="H28" s="10" t="inlineStr"/>
@@ -2286,7 +2286,7 @@
       </c>
       <c r="G29" s="15" t="inlineStr">
         <is>
-          <t>🟡单独训练·未进名单</t>
+          <t>🟡8/13单练·8/15未跟队</t>
         </is>
       </c>
       <c r="H29" s="14" t="inlineStr">
@@ -2320,7 +2320,7 @@
       </c>
       <c r="G30" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·未赴沪</t>
+          <t>🟡8/13单练·8/15未跟队</t>
         </is>
       </c>
       <c r="H30" s="10" t="inlineStr"/>
@@ -2358,7 +2358,7 @@
       </c>
       <c r="G31" s="29" t="inlineStr">
         <is>
-          <t>🟢正常·未赴沪</t>
+          <t>🟢8/13未训练</t>
         </is>
       </c>
       <c r="H31" s="14" t="inlineStr"/>
@@ -2396,7 +2396,7 @@
       </c>
       <c r="G32" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·未赴沪</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H32" s="10" t="inlineStr"/>
@@ -2440,7 +2440,7 @@
       </c>
       <c r="G34" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' RPE=9</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H34" s="10" t="inlineStr"/>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="G35" s="31" t="inlineStr">
         <is>
-          <t>🔴赛前MCL疼·D+2 RPE=5偏高⚠️</t>
+          <t>🟡左后群紧·睡眠4</t>
         </is>
       </c>
       <c r="H35" s="14" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="G36" s="26" t="inlineStr">
         <is>
-          <t>🟢正常·首发95' ⚽进球 RPE=9</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H36" s="23" t="inlineStr"/>
@@ -2540,7 +2540,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>🟢正常·55'替补登场 ⚽进球·趾骨已恢复✅</t>
+          <t>🟢正常</t>
         </is>
       </c>
     </row>
@@ -2577,7 +2577,7 @@
       </c>
       <c r="G38" s="10" t="inlineStr">
         <is>
-          <t>🟢正常·8.5替补24'</t>
+          <t>🟢正常</t>
         </is>
       </c>
       <c r="H38" s="10" t="inlineStr"/>
